--- a/files/九龙-九龙站-天玺.xlsx
+++ b/files/九龙-九龙站-天玺.xlsx
@@ -38992,7 +38992,7 @@
           <t>C | 1775呎 (4+房)
 $23197万
 $130,686/呎
-(25年-08月)</t>
+(25年-08月-25日)</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr">
@@ -39054,7 +39054,7 @@
           <t>A | 1535呎 (4+房)
 $14954万
 $97,423/呎
-(25年-04月)</t>
+(25年-04月-22日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -39093,7 +39093,7 @@
           <t>A | 1535呎 (4+房)
 $14196万
 $92,479/呎
-(23年-04月)</t>
+(23年-04月-11日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -39132,7 +39132,7 @@
           <t>A | 1535呎 (4+房)
 $13190万
 $85,929/呎
-(23年-03月)</t>
+(23年-03月-08日)</t>
         </is>
       </c>
       <c r="C9" s="23" t="inlineStr">
@@ -39171,7 +39171,7 @@
           <t>A | 1451呎 (4+房)
 $12144万
 $83,695/呎
-(22年-08月)</t>
+(22年-08月-23日)</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
@@ -39210,7 +39210,7 @@
           <t>A | 1451呎 (4+房)
 $11066万
 $76,266/呎
-(18年-05月)</t>
+(18年-05月-20日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -39218,7 +39218,7 @@
           <t>B | 678呎 (2房)
 $5178万
 $76,377/呎
-(21年-08月)</t>
+(21年-08月-02日)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -39226,7 +39226,7 @@
           <t>C | 1361呎 (4+房)
 $10518万
 $77,282/呎
-(18年-06月)</t>
+(18年-06月-19日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -39234,7 +39234,7 @@
           <t>D | 1396呎 (4+房)
 $9230万
 $66,115/呎
-(18年-06月)</t>
+(18年-06月-07日)</t>
         </is>
       </c>
     </row>
@@ -39249,7 +39249,7 @@
           <t>A | 1481呎 (4+房)
 $10074万
 $68,019/呎
-(18年-05月)</t>
+(18年-05月-03日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -39257,7 +39257,7 @@
           <t>B | 693呎 (2房)
 $4874万
 $70,339/呎
-(18年-08月)</t>
+(18年-08月-21日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -39265,7 +39265,7 @@
           <t>C | 1377呎 (4+房)
 $9368万
 $68,035/呎
-(18年-05月)</t>
+(18年-05月-16日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -39273,7 +39273,7 @@
           <t>D | 1396呎 (4+房)
 $8704万
 $62,352/呎
-(18年-05月)</t>
+(18年-05月-16日)</t>
         </is>
       </c>
     </row>
@@ -39288,7 +39288,7 @@
           <t>A | 1481呎 (4+房)
 $9473万
 $63,964/呎
-(17年-10月)</t>
+(17年-10月-19日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -39296,7 +39296,7 @@
           <t>B | 693呎 (2房)
 $4584万
 $66,145/呎
-(18年-07月)</t>
+(18年-07月-29日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -39304,7 +39304,7 @@
           <t>C | 1377呎 (4+房)
 $8520万
 $61,870/呎
-(18年-05月)</t>
+(18年-05月-07日)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -39312,7 +39312,7 @@
           <t>D | 1396呎 (4+房)
 $7926万
 $56,773/呎
-(18年-04月)</t>
+(18年-04月-10日)</t>
         </is>
       </c>
     </row>
@@ -39327,7 +39327,7 @@
           <t>A | 1481呎 (4+房)
 $8880万
 $59,962/呎
-(17年-06月)</t>
+(17年-06月-06日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -39335,7 +39335,7 @@
           <t>B | 693呎 (2房)
 $4156万
 $59,964/呎
-(17年-06月)</t>
+(17年-06月-06日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -39343,7 +39343,7 @@
           <t>C | 1377呎 (4+房)
 $8259万
 $59,977/呎
-(17年-10月)</t>
+(17年-10月-10日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -39351,7 +39351,7 @@
           <t>D | 1396呎 (4+房)
 $7440万
 $53,295/呎
-(17年-11月)</t>
+(17年-11月-29日)</t>
         </is>
       </c>
     </row>
@@ -39366,7 +39366,7 @@
           <t>A | 1451呎 (4+房)
 $12397万
 $85,436/呎
-(17年-03月)</t>
+(17年-03月-15日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -39374,7 +39374,7 @@
           <t>B | 678呎 (2房)
 $12397万
 $182,842/呎
-(17年-03月)</t>
+(17年-03月-15日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -39382,7 +39382,7 @@
           <t>C | 1361呎 (4+房)
 $7595万
 $55,805/呎
-(17年-08月)</t>
+(17年-08月-09日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -39390,7 +39390,7 @@
           <t>D | 1396呎 (4+房)
 $7083万
 $50,737/呎
-(17年-05月)</t>
+(17年-05月-03日)</t>
         </is>
       </c>
     </row>
@@ -39405,7 +39405,7 @@
           <t>A | 1481呎 (4+房)
 $11685万
 $78,896/呎
-(16年-11月)</t>
+(16年-11月-01日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -39413,7 +39413,7 @@
           <t>B | 693呎 (2房)
 $11685万
 $168,608/呎
-(16年-11月)</t>
+(16年-11月-01日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -39421,7 +39421,7 @@
           <t>C | 1361呎 (4+房)
 $7159万
 $52,599/呎
-(17年-02月)</t>
+(17年-02月-09日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -39429,7 +39429,7 @@
           <t>D | 1396呎 (4+房)
 $6725万
 $48,175/呎
-(16年-11月)</t>
+(16年-11月-23日)</t>
         </is>
       </c>
     </row>
@@ -39444,7 +39444,7 @@
           <t>A | 1481呎 (4+房)
 $7591万
 $51,258/呎
-(16年-10月)</t>
+(16年-10月-31日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -39452,7 +39452,7 @@
           <t>B | 678呎 (2房)
 $3552万
 $52,395/呎
-(17年-09月)</t>
+(17年-09月-05日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -39460,7 +39460,7 @@
           <t>C | 1361呎 (4+房)
 $7215万
 $53,015/呎
-(16年-11月)</t>
+(16年-11月-16日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -39468,7 +39468,7 @@
           <t>D | 1396呎 (4+房)
 $6414万
 $45,945/呎
-(16年-10月)</t>
+(16年-10月-30日)</t>
         </is>
       </c>
     </row>
@@ -39483,7 +39483,7 @@
           <t>A | 1451呎 (4+房)
 $10899万
 $75,110/呎
-(18年-10月)</t>
+(18年-10月-18日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -39491,7 +39491,7 @@
           <t>B | 678呎 (2房)
 $5100万
 $75,221/呎
-(18年-10月)</t>
+(18年-10月-18日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -39499,7 +39499,7 @@
           <t>C | 1361呎 (4+房)
 $10059万
 $73,906/呎
-(21年-08月)</t>
+(21年-08月-24日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -39507,7 +39507,7 @@
           <t>D | 1396呎 (4+房)
 $8789万
 $62,959/呎
-(23年-06月)</t>
+(23年-06月-14日)</t>
         </is>
       </c>
     </row>
@@ -39522,7 +39522,7 @@
           <t>A | 1451呎 (4+房)
 $7464万
 $51,440/呎
-(16年-04月)</t>
+(16年-04月-07日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -39530,7 +39530,7 @@
           <t>B | 678呎 (2房)
 $3378万
 $49,817/呎
-(17年-10月)</t>
+(17年-10月-30日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -39538,7 +39538,7 @@
           <t>C | 1361呎 (4+房)
 $6713万
 $49,322/呎
-(16年-09月)</t>
+(16年-09月-13日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -39546,7 +39546,7 @@
           <t>D | 1396呎 (4+房)
 $6098万
 $43,685/呎
-(16年-09月)</t>
+(16年-09月-12日)</t>
         </is>
       </c>
     </row>
@@ -39561,7 +39561,7 @@
           <t>A | 1449呎 (4+房)
 $10661万
 $73,572/呎
-(18年-12月)</t>
+(18年-12月-23日)</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
@@ -39577,7 +39577,7 @@
           <t>C | 1356呎 (4+房)
 $9453万
 $69,715/呎
-(23年-12月)</t>
+(23年-12月-21日)</t>
         </is>
       </c>
       <c r="E20" s="23" t="inlineStr">
@@ -39600,7 +39600,7 @@
           <t>A | 1469呎 (4+房)
 $10745万
 $73,148/呎
-(15年-03月)</t>
+(15年-03月-28日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -39608,7 +39608,7 @@
           <t>B | 693呎 (2房)
 $10745万
 $155,056/呎
-(15年-03月)</t>
+(15年-03月-28日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -39616,7 +39616,7 @@
           <t>C | 1356呎 (4+房)
 $6984万
 $51,501/呎
-(15年-07月)</t>
+(15年-07月-15日)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -39624,7 +39624,7 @@
           <t>D | 1396呎 (4+房)
 $6014万
 $43,078/呎
-(15年-06月)</t>
+(15年-06月-03日)</t>
         </is>
       </c>
     </row>
@@ -39639,7 +39639,7 @@
           <t>A | 1463呎 (4+房)
 $10055万
 $68,727/呎
-(18年-09月)</t>
+(18年-09月-25日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -39647,7 +39647,7 @@
           <t>B | 676呎 (2房)
 $4763万
 $70,460/呎
-(18年-09月)</t>
+(18年-09月-19日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -39655,7 +39655,7 @@
           <t>C | 1377呎 (4+房)
 $9466万
 $68,746/呎
-(18年-07月)</t>
+(18年-07月-29日)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -39663,7 +39663,7 @@
           <t>D | 1396呎 (4+房)
 $8489万
 $60,813/呎
-(23年-05月)</t>
+(23年-05月-29日)</t>
         </is>
       </c>
     </row>
@@ -39678,7 +39678,7 @@
           <t>A | 1475呎 (4+房)
 $11165万
 $75,692/呎
-(15年-05月)</t>
+(15年-05月-02日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -39686,7 +39686,7 @@
           <t>B | 693呎 (2房)
 $11165万
 $161,105/呎
-(15年-05月)</t>
+(15年-05月-02日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -39694,7 +39694,7 @@
           <t>C | 1356呎 (4+房)
 $6887万
 $50,787/呎
-(15年-06月)</t>
+(15年-06月-03日)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -39702,7 +39702,7 @@
           <t>D | 1396呎 (4+房)
 $5735万
 $41,082/呎
-(15年-05月)</t>
+(15年-05月-03日)</t>
         </is>
       </c>
     </row>
@@ -39717,7 +39717,7 @@
           <t>A | 1463呎 (4+房)
 $10378万
 $70,939/呎
-(15年-03月)</t>
+(15年-03月-20日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -39725,7 +39725,7 @@
           <t>B | 693呎 (2房)
 $10378万
 $149,761/呎
-(15年-03月)</t>
+(15年-03月-20日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -39733,7 +39733,7 @@
           <t>C | 1356呎 (4+房)
 $6768万
 $49,909/呎
-(15年-04月)</t>
+(15年-04月-14日)</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -39741,7 +39741,7 @@
           <t>D | 1396呎 (4+房)
 $5825万
 $41,724/呎
-(15年-04月)</t>
+(15年-04月-23日)</t>
         </is>
       </c>
     </row>
@@ -39756,7 +39756,7 @@
           <t>A | 1463呎 (4+房)
 $10879万
 $74,360/呎
-(15年-03月)</t>
+(15年-03月-20日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -39764,7 +39764,7 @@
           <t>B | 693呎 (2房)
 $10879万
 $156,983/呎
-(15年-03月)</t>
+(15年-03月-20日)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -39772,7 +39772,7 @@
           <t>C | 1377呎 (4+房)
 $6438万
 $46,752/呎
-(15年-06月)</t>
+(15年-06月-04日)</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
@@ -39780,7 +39780,7 @@
           <t>D | 1396呎 (4+房)
 $6105万
 $43,735/呎
-(15年-04月)</t>
+(15年-04月-16日)</t>
         </is>
       </c>
     </row>
@@ -39795,7 +39795,7 @@
           <t>A | 1443呎 (4+房)
 $10306万
 $71,423/呎
-(15年-03月)</t>
+(15年-03月-20日)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -39803,7 +39803,7 @@
           <t>B | 676呎 (2房)
 $10306万
 $152,461/呎
-(15年-03月)</t>
+(15年-03月-20日)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -39811,7 +39811,7 @@
           <t>C | 1356呎 (4+房)
 $6721万
 $49,563/呎
-(15年-04月)</t>
+(15年-04月-23日)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -39819,7 +39819,7 @@
           <t>D | 1396呎 (4+房)
 $6105万
 $43,735/呎
-(15年-04月)</t>
+(15年-04月-23日)</t>
         </is>
       </c>
     </row>
@@ -39834,7 +39834,7 @@
           <t>A | 1463呎 (4+房)
 $10729万
 $73,334/呎
-(15年-03月)</t>
+(15年-03月-20日)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -39842,7 +39842,7 @@
           <t>B | 693呎 (2房)
 $10729万
 $154,816/呎
-(15年-03月)</t>
+(15年-03月-20日)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -39850,7 +39850,7 @@
           <t>C | 1356呎 (4+房)
 $6349万
 $46,820/呎
-(15年-07月)</t>
+(15年-07月-02日)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -39858,7 +39858,7 @@
           <t>D | 1396呎 (4+房)
 $5704万
 $40,861/呎
-(15年-04月)</t>
+(15年-04月-22日)</t>
         </is>
       </c>
     </row>
@@ -40003,7 +40003,7 @@
           <t>B | 1352呎 (4+房)
 $2941万
 $21,751/呎
-(09年-03月)</t>
+(09年-03月-26日)</t>
         </is>
       </c>
       <c r="D5" s="22" t="inlineStr">
@@ -40011,7 +40011,7 @@
           <t>C | 1130呎 (3房)
 $2926万
 $25,891/呎
-(09年-04月)</t>
+(09年-04月-06日)</t>
         </is>
       </c>
       <c r="E5" s="21" t="inlineStr"/>
@@ -40020,7 +40020,7 @@
           <t>E | 670呎 (2房)
 $1188万
 $17,726/呎
-(09年-04月)</t>
+(09年-04月-26日)</t>
         </is>
       </c>
     </row>
@@ -40036,7 +40036,7 @@
           <t>B | 1333呎 (4+房)
 $3632万
 $27,247/呎
-(09年-03月)</t>
+(09年-03月-30日)</t>
         </is>
       </c>
       <c r="D6" s="22" t="inlineStr">
@@ -40044,7 +40044,7 @@
           <t>C | 664呎 (2房)
 $1235万
 $18,596/呎
-(09年-04月)</t>
+(09年-04月-06日)</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
@@ -40052,7 +40052,7 @@
           <t>D | 672呎 (2房)
 $1187万
 $17,667/呎
-(09年-04月)</t>
+(09年-04月-01日)</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
@@ -40060,7 +40060,7 @@
           <t>E | 670呎 (2房)
 $2300万
 $34,328/呎
-(21年-10月)</t>
+(21年-10月-04日)</t>
         </is>
       </c>
     </row>
@@ -40075,7 +40075,7 @@
           <t>A | 952呎 (3房)
 $1768万
 $18,574/呎
-(09年-03月)</t>
+(09年-03月-23日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -40091,7 +40091,7 @@
           <t>C | 664呎 (2房)
 $1211万
 $18,238/呎
-(09年-03月)</t>
+(09年-03月-26日)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -40099,7 +40099,7 @@
           <t>D | 672呎 (2房)
 $1185万
 $17,641/呎
-(09年-03月)</t>
+(09年-03月-25日)</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr">
@@ -40107,7 +40107,7 @@
           <t>E | 670呎 (2房)
 $1164万
 $17,370/呎
-(09年-03月)</t>
+(09年-03月-25日)</t>
         </is>
       </c>
     </row>
@@ -40122,7 +40122,7 @@
           <t>A | 915呎 (3房)
 $1701万
 $18,590/呎
-(09年-03月)</t>
+(09年-03月-23日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -40130,7 +40130,7 @@
           <t>B | 1117呎 (4+房)
 $2131万
 $19,077/呎
-(09年-04月)</t>
+(09年-04月-20日)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -40138,7 +40138,7 @@
           <t>C | 664呎 (2房)
 $1230万
 $18,530/呎
-(09年-03月)</t>
+(09年-03月-23日)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -40146,7 +40146,7 @@
           <t>D | 678呎 (2房)
 $1177万
 $17,354/呎
-(09年-03月)</t>
+(09年-03月-22日)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
@@ -40154,7 +40154,7 @@
           <t>E | 670呎 (2房)
 $1162万
 $17,344/呎
-(09年-03月)</t>
+(09年-03月-23日)</t>
         </is>
       </c>
     </row>
@@ -40169,7 +40169,7 @@
           <t>A | 915呎 (3房)
 $1697万
 $18,549/呎
-(09年-03月)</t>
+(09年-03月-22日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -40177,7 +40177,7 @@
           <t>B | 1117呎 (4+房)
 $2116万
 $18,939/呎
-(09年-03月)</t>
+(09年-03月-26日)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -40185,7 +40185,7 @@
           <t>C | 664呎 (2房)
 $1222万
 $18,397/呎
-(09年-03月)</t>
+(09年-03月-22日)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -40193,7 +40193,7 @@
           <t>D | 672呎 (2房)
 $1175万
 $17,482/呎
-(09年-03月)</t>
+(09年-03月-26日)</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
@@ -40201,7 +40201,7 @@
           <t>E | 670呎 (2房)
 $1159万
 $17,304/呎
-(09年-03月)</t>
+(09年-03月-23日)</t>
         </is>
       </c>
     </row>
@@ -40216,7 +40216,7 @@
           <t>A | 915呎 (3房)
 $1692万
 $18,493/呎
-(09年-03月)</t>
+(09年-03月-25日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -40224,7 +40224,7 @@
           <t>B | 1117呎 (4+房)
 $2116万
 $18,939/呎
-(09年-03月)</t>
+(09年-03月-25日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -40232,7 +40232,7 @@
           <t>C | 664呎 (2房)
 $1217万
 $18,328/呎
-(09年-03月)</t>
+(09年-03月-26日)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -40240,7 +40240,7 @@
           <t>D | 672呎 (2房)
 $1171万
 $17,430/呎
-(09年-04月)</t>
+(09年-04月-01日)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -40248,7 +40248,7 @@
           <t>E | 670呎 (2房)
 $1158万
 $17,291/呎
-(09年-03月)</t>
+(09年-03月-22日)</t>
         </is>
       </c>
     </row>
@@ -40263,7 +40263,7 @@
           <t>A | 915呎 (3房)
 $1690万
 $18,466/呎
-(09年-03月)</t>
+(09年-03月-26日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -40271,7 +40271,7 @@
           <t>B | 1117呎 (4+房)
 $2116万
 $18,939/呎
-(09年-04月)</t>
+(09年-04月-01日)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -40279,7 +40279,7 @@
           <t>C | 664呎 (2房)
 $1213万
 $18,264/呎
-(09年-03月)</t>
+(09年-03月-26日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -40287,7 +40287,7 @@
           <t>D | 672呎 (2房)
 $1170万
 $17,404/呎
-(09年-04月)</t>
+(09年-04月-01日)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -40295,7 +40295,7 @@
           <t>E | 670呎 (2房)
 $1158万
 $17,278/呎
-(09年-03月)</t>
+(09年-03月-22日)</t>
         </is>
       </c>
     </row>
@@ -40310,7 +40310,7 @@
           <t>A | 915呎 (3房)
 $1682万
 $18,384/呎
-(09年-04月)</t>
+(09年-04月-01日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -40318,7 +40318,7 @@
           <t>B | 1117呎 (4+房)
 $2108万
 $18,870/呎
-(09年-03月)</t>
+(09年-03月-25日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -40326,7 +40326,7 @@
           <t>C | 664呎 (2房)
 $1208万
 $18,198/呎
-(09年-03月)</t>
+(09年-03月-25日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -40334,7 +40334,7 @@
           <t>D | 672呎 (2房)
 $1168万
 $17,377/呎
-(09年-03月)</t>
+(09年-03月-26日)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -40342,7 +40342,7 @@
           <t>E | 670呎 (2房)
 $1157万
 $17,265/呎
-(09年-03月)</t>
+(09年-03月-25日)</t>
         </is>
       </c>
     </row>
@@ -40357,7 +40357,7 @@
           <t>A | 915呎 (3房)
 $1676万
 $18,315/呎
-(09年-04月)</t>
+(09年-04月-01日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -40365,7 +40365,7 @@
           <t>B | 1117呎 (4+房)
 $2102万
 $18,816/呎
-(09年-04月)</t>
+(09年-04月-01日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -40373,7 +40373,7 @@
           <t>C | 664呎 (2房)
 $1204万
 $18,131/呎
-(09年-04月)</t>
+(09年-04月-26日)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -40381,7 +40381,7 @@
           <t>D | 672呎 (2房)
 $1163万
 $17,311/呎
-(09年-03月)</t>
+(09年-03月-25日)</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -40389,7 +40389,7 @@
           <t>E | 670呎 (2房)
 $1156万
 $17,251/呎
-(09年-03月)</t>
+(09年-03月-26日)</t>
         </is>
       </c>
     </row>
@@ -40404,7 +40404,7 @@
           <t>A | 915呎 (3房)
 $1676万
 $18,315/呎
-(09年-04月)</t>
+(09年-04月-01日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -40412,7 +40412,7 @@
           <t>B | 1117呎 (4+房)
 $2102万
 $18,816/呎
-(09年-03月)</t>
+(09年-03月-26日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -40420,7 +40420,7 @@
           <t>C | 664呎 (2房)
 $1204万
 $18,131/呎
-(09年-03月)</t>
+(09年-03月-25日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -40428,7 +40428,7 @@
           <t>D | 672呎 (2房)
 $1161万
 $17,272/呎
-(09年-03月)</t>
+(09年-03月-25日)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -40436,7 +40436,7 @@
           <t>E | 676呎 (2房)
 $1153万
 $17,059/呎
-(09年-03月)</t>
+(09年-03月-25日)</t>
         </is>
       </c>
     </row>
@@ -40451,7 +40451,7 @@
           <t>A | 915呎 (3房)
 $1673万
 $18,286/呎
-(09年-03月)</t>
+(09年-03月-22日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -40459,7 +40459,7 @@
           <t>B | 1117呎 (4+房)
 $2100万
 $18,802/呎
-(09年-03月)</t>
+(09年-03月-25日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -40467,7 +40467,7 @@
           <t>C | 664呎 (2房)
 $1191万
 $17,932/呎
-(09年-03月)</t>
+(09年-03月-26日)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -40483,7 +40483,7 @@
           <t>E | 670呎 (2房)
 $1150万
 $17,172/呎
-(09年-03月)</t>
+(09年-03月-29日)</t>
         </is>
       </c>
     </row>
@@ -40498,7 +40498,7 @@
           <t>A | 915呎 (3房)
 $1668万
 $18,232/呎
-(09年-04月)</t>
+(09年-04月-01日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -40506,7 +40506,7 @@
           <t>B | 1117呎 (4+房)
 $2097万
 $18,775/呎
-(09年-03月)</t>
+(09年-03月-26日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -40514,7 +40514,7 @@
           <t>C | 664呎 (2房)
 $1182万
 $17,799/呎
-(09年-03月)</t>
+(09年-03月-26日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -40522,7 +40522,7 @@
           <t>D | 672呎 (2房)
 $1156万
 $17,206/呎
-(09年-03月)</t>
+(09年-03月-24日)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -40530,7 +40530,7 @@
           <t>E | 670呎 (2房)
 $1150万
 $17,159/呎
-(09年-03月)</t>
+(09年-03月-23日)</t>
         </is>
       </c>
     </row>
@@ -40545,7 +40545,7 @@
           <t>A | 915呎 (3房)
 $1663万
 $18,177/呎
-(09年-04月)</t>
+(09年-04月-26日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -40553,7 +40553,7 @@
           <t>B | 1117呎 (4+房)
 $2093万
 $18,734/呎
-(09年-03月)</t>
+(09年-03月-25日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -40561,7 +40561,7 @@
           <t>C | 664呎 (2房)
 $1050万
 $15,819/呎
-(09年-03月)</t>
+(09年-03月-29日)</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
@@ -40592,7 +40592,7 @@
           <t>A | 915呎 (3房)
 $1660万
 $18,142/呎
-(09年-03月)</t>
+(09年-03月-26日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -40600,7 +40600,7 @@
           <t>B | 1117呎 (4+房)
 $2088万
 $18,692/呎
-(09年-03月)</t>
+(09年-03月-22日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -40608,7 +40608,7 @@
           <t>C | 664呎 (2房)
 $1048万
 $15,776/呎
-(09年-03月)</t>
+(09年-03月-29日)</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -40624,7 +40624,7 @@
           <t>E | 670呎 (2房)
 $2455万
 $36,638/呎
-(13年-02月)</t>
+(13年-02月-05日)</t>
         </is>
       </c>
     </row>
@@ -40639,7 +40639,7 @@
           <t>A | 915呎 (3房)
 $1659万
 $18,136/呎
-(09年-03月)</t>
+(09年-03月-23日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -40647,7 +40647,7 @@
           <t>B | 1117呎 (4+房)
 $2085万
 $18,665/呎
-(09年-03月)</t>
+(09年-03月-26日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -40655,7 +40655,7 @@
           <t>C | 664呎 (2房)
 $1045万
 $15,733/呎
-(09年-03月)</t>
+(09年-03月-17日)</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
@@ -40671,7 +40671,7 @@
           <t>E | 670呎 (2房)
 $2384万
 $35,584/呎
-(12年-05月)</t>
+(12年-05月-24日)</t>
         </is>
       </c>
     </row>
@@ -40686,7 +40686,7 @@
           <t>A | 945呎 (3房)
 $1656万
 $17,520/呎
-(09年-04月)</t>
+(09年-04月-19日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -40694,7 +40694,7 @@
           <t>B | 1117呎 (4+房)
 $2080万
 $18,624/呎
-(09年-04月)</t>
+(09年-04月-01日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -40702,7 +40702,7 @@
           <t>C | 675呎 (2房)
 $1042万
 $15,436/呎
-(09年-03月)</t>
+(09年-03月-25日)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
@@ -40718,7 +40718,7 @@
           <t>E | 676呎 (2房)
 $2358万
 $34,876/呎
-(11年-09月)</t>
+(11年-09月-27日)</t>
         </is>
       </c>
     </row>
@@ -40733,7 +40733,7 @@
           <t>A | 915呎 (3房)
 $1652万
 $18,053/呎
-(09年-03月)</t>
+(09年-03月-30日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -40741,7 +40741,7 @@
           <t>B | 1117呎 (4+房)
 $2079万
 $18,610/呎
-(09年-03月)</t>
+(09年-03月-19日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -40749,7 +40749,7 @@
           <t>C | 664呎 (2房)
 $1039万
 $15,649/呎
-(09年-03月)</t>
+(09年-03月-15日)</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr">
@@ -40765,7 +40765,7 @@
           <t>E | 670呎 (2房)
 $2296万
 $34,266/呎
-(12年-05月)</t>
+(12年-05月-27日)</t>
         </is>
       </c>
     </row>
@@ -40780,7 +40780,7 @@
           <t>A | 915呎 (3房)
 $1651万
 $18,039/呎
-(09年-04月)</t>
+(09年-04月-02日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -40788,7 +40788,7 @@
           <t>B | 1117呎 (4+房)
 $2076万
 $18,583/呎
-(09年-03月)</t>
+(09年-03月-25日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -40796,7 +40796,7 @@
           <t>C | 664呎 (2房)
 $2107万
 $31,728/呎
-(13年-11月)</t>
+(13年-11月-26日)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
@@ -40812,7 +40812,7 @@
           <t>E | 670呎 (2房)
 $2234万
 $33,343/呎
-(11年-06月)</t>
+(11年-06月-27日)</t>
         </is>
       </c>
     </row>
@@ -40835,7 +40835,7 @@
           <t>B | 1117呎 (4+房)
 $2076万
 $18,583/呎
-(09年-03月)</t>
+(09年-03月-22日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -40843,7 +40843,7 @@
           <t>C | 664呎 (2房)
 $2089万
 $31,454/呎
-(13年-11月)</t>
+(13年-11月-26日)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
@@ -40859,7 +40859,7 @@
           <t>E | 670呎 (2房)
 $2234万
 $33,343/呎
-(12年-05月)</t>
+(12年-05月-28日)</t>
         </is>
       </c>
     </row>
@@ -40874,7 +40874,7 @@
           <t>A | 915呎 (3房)
 $1648万
 $18,012/呎
-(09年-04月)</t>
+(09年-04月-01日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -40882,7 +40882,7 @@
           <t>B | 1150呎 (4+房)
 $2073万
 $18,023/呎
-(09年-03月)</t>
+(09年-03月-25日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -40890,7 +40890,7 @@
           <t>C | 664呎 (2房)
 $2049万
 $30,856/呎
-(13年-11月)</t>
+(13年-11月-26日)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
@@ -40906,7 +40906,7 @@
           <t>E | 670呎 (2房)
 $2128万
 $31,762/呎
-(11年-06月)</t>
+(11年-06月-15日)</t>
         </is>
       </c>
     </row>
@@ -40921,7 +40921,7 @@
           <t>A | 915呎 (3房)
 $1632万
 $17,833/呎
-(09年-03月)</t>
+(09年-03月-29日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -40929,7 +40929,7 @@
           <t>B | 1117呎 (4+房)
 $2073万
 $18,555/呎
-(09年-03月)</t>
+(09年-03月-18日)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -40937,7 +40937,7 @@
           <t>C | 664呎 (2房)
 $2027万
 $30,534/呎
-(13年-11月)</t>
+(13年-11月-28日)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
@@ -40953,7 +40953,7 @@
           <t>E | 670呎 (2房)
 $2066万
 $30,839/呎
-(12年-04月)</t>
+(12年-04月-17日)</t>
         </is>
       </c>
     </row>
@@ -40977,7 +40977,7 @@
           <t>C | 664呎 (2房)
 $1989万
 $29,954/呎
-(13年-11月)</t>
+(13年-11月-26日)</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
@@ -40993,7 +40993,7 @@
           <t>E | 670呎 (2房)
 $1987万
 $29,653/呎
-(11年-05月)</t>
+(11年-05月-16日)</t>
         </is>
       </c>
     </row>
@@ -41008,7 +41008,7 @@
           <t>A | 2581呎 (4+房)
 $9592万
 $37,164/呎
-(09年-03月)</t>
+(09年-03月-19日)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -41016,7 +41016,7 @@
           <t>B | 1107呎 (4+房)
 $3060万
 $27,642/呎
-(09年-04月)</t>
+(09年-04月-05日)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -41024,7 +41024,7 @@
           <t>C | 664呎 (2房)
 $1951万
 $29,384/呎
-(13年-11月)</t>
+(13年-11月-26日)</t>
         </is>
       </c>
       <c r="E27" s="20" t="inlineStr">
@@ -41217,7 +41217,7 @@
           <t>A | 1679呎 (4+房)
 $15281万
 $91,014/呎
-(25年-02月)</t>
+(25年-02月-19日)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -41225,7 +41225,7 @@
           <t>B | 1301呎 (4+房)
 $3294万
 $25,317/呎
-(09年-04月)</t>
+(09年-04月-06日)</t>
         </is>
       </c>
       <c r="D6" s="22" t="inlineStr">
@@ -41233,7 +41233,7 @@
           <t>C | 1035呎 (3房)
 $2513万
 $24,278/呎
-(09年-03月)</t>
+(09年-03月-17日)</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
@@ -41241,7 +41241,7 @@
           <t>D | 906呎 (3房)
 $2055万
 $22,683/呎
-(09年-03月)</t>
+(09年-03月-25日)</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
@@ -41249,7 +41249,7 @@
           <t>E | 1279呎 (3房)
 $3442万
 $26,912/呎
-(09年-03月)</t>
+(09年-03月-26日)</t>
         </is>
       </c>
     </row>
@@ -41264,7 +41264,7 @@
           <t>A | 1605呎 (4+房)
 $13736万
 $85,583/呎
-(24年-10月)</t>
+(24年-10月-27日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -41272,7 +41272,7 @@
           <t>B | 1301呎 (4+房)
 $3250万
 $24,980/呎
-(09年-03月)</t>
+(09年-03月-26日)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -41280,7 +41280,7 @@
           <t>C | 1035呎 (3房)
 $2478万
 $23,941/呎
-(09年-03月)</t>
+(09年-03月-24日)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -41288,7 +41288,7 @@
           <t>D | 906呎 (3房)
 $2028万
 $22,382/呎
-(09年-03月)</t>
+(09年-03月-25日)</t>
         </is>
       </c>
       <c r="F7" s="20" t="inlineStr">
@@ -41311,7 +41311,7 @@
           <t>A | 1679呎 (4+房)
 $7986万
 $47,563/呎
-(10年-10月)</t>
+(10年-10月-24日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -41319,7 +41319,7 @@
           <t>B | 1301呎 (4+房)
 $3241万
 $24,913/呎
-(09年-03月)</t>
+(09年-03月-26日)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -41327,7 +41327,7 @@
           <t>C | 1035呎 (3房)
 $2464万
 $23,806/呎
-(09年-03月)</t>
+(09年-03月-24日)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -41335,7 +41335,7 @@
           <t>D | 906呎 (3房)
 $2015万
 $22,246/呎
-(09年-03月)</t>
+(09年-03月-30日)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
@@ -41343,7 +41343,7 @@
           <t>E | 1279呎 (3房)
 $3200万
 $25,020/呎
-(09年-04月)</t>
+(09年-04月-06日)</t>
         </is>
       </c>
     </row>
@@ -41358,7 +41358,7 @@
           <t>A | 1717呎 (4+房)
 $9356万
 $54,490/呎
-(12年-04月)</t>
+(12年-04月-29日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -41366,7 +41366,7 @@
           <t>B | 1301呎 (4+房)
 $3171万
 $24,374/呎
-(09年-03月)</t>
+(09年-03月-24日)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -41374,7 +41374,7 @@
           <t>C | 1035呎 (3房)
 $2422万
 $23,402/呎
-(09年-03月)</t>
+(09年-03月-17日)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -41382,7 +41382,7 @@
           <t>D | 906呎 (3房)
 $2006万
 $22,136/呎
-(09年-03月)</t>
+(09年-03月-30日)</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
@@ -41390,7 +41390,7 @@
           <t>E | 1279呎 (3房)
 $3098万
 $24,220/呎
-(09年-04月)</t>
+(09年-04月-26日)</t>
         </is>
       </c>
     </row>
@@ -41405,7 +41405,7 @@
           <t>A | 1679呎 (4+房)
 $6066万
 $36,128/呎
-(09年-04月)</t>
+(09年-04月-26日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -41413,7 +41413,7 @@
           <t>B | 1301呎 (4+房)
 $3159万
 $24,280/呎
-(09年-03月)</t>
+(09年-03月-26日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -41421,7 +41421,7 @@
           <t>C | 1035呎 (3房)
 $2400万
 $23,187/呎
-(09年-03月)</t>
+(09年-03月-17日)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -41429,7 +41429,7 @@
           <t>D | 905呎 (3房)
 $1930万
 $21,323/呎
-(09年-03月)</t>
+(09年-03月-22日)</t>
         </is>
       </c>
       <c r="F10" s="21" t="inlineStr"/>
@@ -41445,7 +41445,7 @@
           <t>A | 1679呎 (4+房)
 $5975万
 $35,586/呎
-(09年-07月)</t>
+(09年-07月-14日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -41453,7 +41453,7 @@
           <t>B | 1301呎 (4+房)
 $3148万
 $24,199/呎
-(09年-03月)</t>
+(09年-03月-22日)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -41461,7 +41461,7 @@
           <t>C | 1035呎 (3房)
 $2392万
 $23,108/呎
-(09年-03月)</t>
+(09年-03月-15日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -41469,7 +41469,7 @@
           <t>D | 905呎 (3房)
 $1924万
 $21,255/呎
-(09年-03月)</t>
+(09年-03月-15日)</t>
         </is>
       </c>
       <c r="F11" s="21" t="inlineStr"/>
@@ -41485,7 +41485,7 @@
           <t>A | 1679呎 (4+房)
 $6280万
 $37,403/呎
-(09年-10月)</t>
+(09年-10月-06日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -41493,7 +41493,7 @@
           <t>B | 1314呎 (4+房)
 $3133万
 $23,840/呎
-(09年-03月)</t>
+(09年-03月-17日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -41501,7 +41501,7 @@
           <t>C | 1035呎 (3房)
 $2382万
 $23,013/呎
-(09年-03月)</t>
+(09年-03月-17日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -41509,7 +41509,7 @@
           <t>D | 905呎 (3房)
 $1911万
 $21,117/呎
-(09年-03月)</t>
+(09年-03月-26日)</t>
         </is>
       </c>
       <c r="F12" s="21" t="inlineStr"/>
@@ -41525,7 +41525,7 @@
           <t>A | 1942呎 (4+房)
 $13145万
 $67,688/呎
-(12年-09月)</t>
+(12年-09月-06日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -41533,7 +41533,7 @@
           <t>B | 1301呎 (4+房)
 $3119万
 $23,970/呎
-(09年-03月)</t>
+(09年-03月-17日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -41541,7 +41541,7 @@
           <t>C | 1035呎 (3房)
 $2359万
 $22,795/呎
-(09年-03月)</t>
+(09年-03月-09日)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -41549,7 +41549,7 @@
           <t>D | 894呎 (3房)
 $1854万
 $20,743/呎
-(09年-03月)</t>
+(09年-03月-15日)</t>
         </is>
       </c>
       <c r="F13" s="21" t="inlineStr"/>
@@ -41565,7 +41565,7 @@
           <t>A | 1530呎 (4+房)
 $4181万
 $27,329/呎
-(09年-03月)</t>
+(09年-03月-26日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -41573,7 +41573,7 @@
           <t>B | 1314呎 (4+房)
 $3084万
 $23,467/呎
-(09年-03月)</t>
+(09年-03月-22日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -41581,7 +41581,7 @@
           <t>C | 1019呎 (3房)
 $2322万
 $22,785/呎
-(09年-03月)</t>
+(09年-03月-22日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -41589,7 +41589,7 @@
           <t>D | 885呎 (3房)
 $1850万
 $20,902/呎
-(09年-03月)</t>
+(09年-03月-18日)</t>
         </is>
       </c>
       <c r="F14" s="21" t="inlineStr"/>
@@ -41605,7 +41605,7 @@
           <t>A | 1530呎 (4+房)
 $4140万
 $27,059/呎
-(09年-03月)</t>
+(09年-03月-19日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -41613,7 +41613,7 @@
           <t>B | 1295呎 (4+房)
 $3031万
 $23,405/呎
-(09年-03月)</t>
+(09年-03月-19日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -41621,7 +41621,7 @@
           <t>C | 1019呎 (3房)
 $2294万
 $22,513/呎
-(09年-03月)</t>
+(09年-03月-12日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -41629,7 +41629,7 @@
           <t>D | 910呎 (3房)
 $1832万
 $20,128/呎
-(09年-03月)</t>
+(09年-03月-11日)</t>
         </is>
       </c>
       <c r="F15" s="21" t="inlineStr"/>
@@ -41645,7 +41645,7 @@
           <t>A | 1530呎 (4+房)
 $4099万
 $26,788/呎
-(09年-04月)</t>
+(09年-04月-01日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -41653,7 +41653,7 @@
           <t>B | 1295呎 (4+房)
 $3031万
 $23,405/呎
-(09年-03月)</t>
+(09年-03月-19日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -41661,7 +41661,7 @@
           <t>C | 1019呎 (3房)
 $2282万
 $22,394/呎
-(09年-03月)</t>
+(09年-03月-16日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -41669,7 +41669,7 @@
           <t>D | 885呎 (3房)
 $1820万
 $20,559/呎
-(09年-03月)</t>
+(09年-03月-25日)</t>
         </is>
       </c>
       <c r="F16" s="21" t="inlineStr"/>
@@ -41685,7 +41685,7 @@
           <t>A | 1530呎 (4+房)
 $4099万
 $26,788/呎
-(09年-03月)</t>
+(09年-03月-15日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -41693,7 +41693,7 @@
           <t>B | 1295呎 (4+房)
 $3013万
 $23,270/呎
-(09年-03月)</t>
+(09年-03月-15日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -41701,7 +41701,7 @@
           <t>C | 1019呎 (3房)
 $2282万
 $22,394/呎
-(09年-03月)</t>
+(09年-03月-12日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -41709,7 +41709,7 @@
           <t>D | 885呎 (3房)
 $1801万
 $20,354/呎
-(09年-03月)</t>
+(09年-03月-16日)</t>
         </is>
       </c>
       <c r="F17" s="21" t="inlineStr"/>
@@ -41725,7 +41725,7 @@
           <t>A | 1530呎 (4+房)
 $4074万
 $26,626/呎
-(09年-03月)</t>
+(09年-03月-17日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -41733,7 +41733,7 @@
           <t>B | 1295呎 (4+房)
 $2970万
 $22,934/呎
-(09年-03月)</t>
+(09年-03月-17日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -41741,7 +41741,7 @@
           <t>C | 1019呎 (3房)
 $2247万
 $22,047/呎
-(09年-03月)</t>
+(09年-03月-17日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -41749,7 +41749,7 @@
           <t>D | 885呎 (3房)
 $1783万
 $20,148/呎
-(09年-03月)</t>
+(09年-03月-19日)</t>
         </is>
       </c>
       <c r="F18" s="21" t="inlineStr"/>
@@ -41765,7 +41765,7 @@
           <t>A | 1530呎 (4+房)
 $4041万
 $26,409/呎
-(09年-03月)</t>
+(09年-03月-24日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -41773,7 +41773,7 @@
           <t>B | 1295呎 (4+房)
 $2943万
 $22,729/呎
-(09年-03月)</t>
+(09年-03月-09日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -41781,7 +41781,7 @@
           <t>C | 1019呎 (3房)
 $2229万
 $21,873/呎
-(09年-03月)</t>
+(09年-03月-10日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -41789,7 +41789,7 @@
           <t>D | 885呎 (3房)
 $1771万
 $20,011/呎
-(09年-03月)</t>
+(09年-03月-11日)</t>
         </is>
       </c>
       <c r="F19" s="21" t="inlineStr"/>
@@ -41805,7 +41805,7 @@
           <t>A | 1530呎 (4+房)
 $4016万
 $26,247/呎
-(09年-03月)</t>
+(09年-03月-17日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -41813,7 +41813,7 @@
           <t>B | 1295呎 (4+房)
 $2917万
 $22,526/呎
-(09年-03月)</t>
+(09年-03月-24日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -41821,7 +41821,7 @@
           <t>C | 1019呎 (3房)
 $2211万
 $21,700/呎
-(09年-03月)</t>
+(09年-03月-17日)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -41829,7 +41829,7 @@
           <t>D | 885呎 (3房)
 $1765万
 $19,943/呎
-(09年-03月)</t>
+(09年-03月-24日)</t>
         </is>
       </c>
       <c r="F20" s="21" t="inlineStr"/>
@@ -41845,7 +41845,7 @@
           <t>A | 1530呎 (4+房)
 $3991万
 $26,085/呎
-(09年-03月)</t>
+(09年-03月-23日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -41853,7 +41853,7 @@
           <t>B | 1295呎 (4+房)
 $2887万
 $22,296/呎
-(09年-03月)</t>
+(09年-03月-19日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -41861,7 +41861,7 @@
           <t>C | 1019呎 (3房)
 $2194万
 $21,526/呎
-(09年-03月)</t>
+(09年-03月-12日)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -41869,7 +41869,7 @@
           <t>D | 885呎 (3房)
 $1759万
 $19,874/呎
-(09年-03月)</t>
+(09年-03月-23日)</t>
         </is>
       </c>
       <c r="F21" s="21" t="inlineStr"/>
@@ -41885,7 +41885,7 @@
           <t>A | 1530呎 (4+房)
 $3966万
 $25,922/呎
-(09年-03月)</t>
+(09年-03月-17日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -41893,7 +41893,7 @@
           <t>B | 1295呎 (4+房)
 $2873万
 $22,185/呎
-(09年-03月)</t>
+(09年-03月-25日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -41901,7 +41901,7 @@
           <t>C | 1019呎 (3房)
 $2176万
 $21,353/呎
-(09年-03月)</t>
+(09年-03月-17日)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -41909,7 +41909,7 @@
           <t>D | 885呎 (3房)
 $1747万
 $19,737/呎
-(09年-03月)</t>
+(09年-03月-30日)</t>
         </is>
       </c>
       <c r="F22" s="21" t="inlineStr"/>
@@ -41925,7 +41925,7 @@
           <t>A | 1530呎 (4+房)
 $3941万
 $25,760/呎
-(09年-03月)</t>
+(09年-03月-09日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -41933,7 +41933,7 @@
           <t>B | 1295呎 (4+房)
 $2847万
 $21,985/呎
-(09年-03月)</t>
+(09年-03月-12日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -41941,7 +41941,7 @@
           <t>C | 1019呎 (3房)
 $2158万
 $21,179/呎
-(09年-03月)</t>
+(09年-03月-16日)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -41949,7 +41949,7 @@
           <t>D | 885呎 (3房)
 $1735万
 $19,600/呎
-(09年-03月)</t>
+(09年-03月-16日)</t>
         </is>
       </c>
       <c r="F23" s="21" t="inlineStr"/>
@@ -41965,7 +41965,7 @@
           <t>A | 1530呎 (4+房)
 $3912万
 $25,571/呎
-(09年-03月)</t>
+(09年-03月-26日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -41973,7 +41973,7 @@
           <t>B | 1295呎 (4+房)
 $2821万
 $21,782/呎
-(09年-03月)</t>
+(09年-03月-17日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -41981,7 +41981,7 @@
           <t>C | 1019呎 (3房)
 $2140万
 $21,005/呎
-(09年-03月)</t>
+(09年-03月-17日)</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -41989,7 +41989,7 @@
           <t>D | 910呎 (3房)
 $1729万
 $18,995/呎
-(09年-03月)</t>
+(09年-03月-26日)</t>
         </is>
       </c>
       <c r="F24" s="21" t="inlineStr"/>
@@ -42005,7 +42005,7 @@
           <t>A | 1530呎 (4+房)
 $3888万
 $25,412/呎
-(09年-03月)</t>
+(09年-03月-11日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -42013,7 +42013,7 @@
           <t>B | 1295呎 (4+房)
 $2803万
 $21,646/呎
-(09年-03月)</t>
+(09年-03月-15日)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -42021,7 +42021,7 @@
           <t>C | 1019呎 (3房)
 $2123万
 $20,832/呎
-(09年-03月)</t>
+(09年-03月-09日)</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
@@ -42029,7 +42029,7 @@
           <t>D | 885呎 (3房)
 $1722万
 $19,463/呎
-(09年-03月)</t>
+(09年-03月-24日)</t>
         </is>
       </c>
       <c r="F25" s="21" t="inlineStr"/>
@@ -42045,7 +42045,7 @@
           <t>A | 1530呎 (4+房)
 $3888万
 $25,412/呎
-(09年-03月)</t>
+(09年-03月-17日)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -42053,7 +42053,7 @@
           <t>B | 1295呎 (4+房)
 $2803万
 $21,646/呎
-(09年-03月)</t>
+(09年-03月-17日)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -42061,7 +42061,7 @@
           <t>C | 1019呎 (3房)
 $2123万
 $20,832/呎
-(09年-03月)</t>
+(09年-03月-10日)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -42069,7 +42069,7 @@
           <t>D | 885呎 (3房)
 $1710万
 $19,326/呎
-(09年-03月)</t>
+(09年-03月-19日)</t>
         </is>
       </c>
       <c r="F26" s="21" t="inlineStr"/>
@@ -42085,7 +42085,7 @@
           <t>A | 1530呎 (4+房)
 $3836万
 $25,070/呎
-(09年-03月)</t>
+(09年-03月-15日)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -42093,7 +42093,7 @@
           <t>B | 1295呎 (4+房)
 $2716万
 $20,970/呎
-(09年-03月)</t>
+(09年-03月-19日)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -42101,7 +42101,7 @@
           <t>C | 1019呎 (3房)
 $2114万
 $20,750/呎
-(09年-03月)</t>
+(09年-03月-09日)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -42109,7 +42109,7 @@
           <t>D | 885呎 (3房)
 $1698万
 $19,189/呎
-(09年-03月)</t>
+(09年-03月-09日)</t>
         </is>
       </c>
       <c r="F27" s="21" t="inlineStr"/>
@@ -42284,7 +42284,7 @@
           <t>A | 640呎 (2房)
 $1100万
 $17,188/呎
-(09年-04月)</t>
+(09年-04月-01日)</t>
         </is>
       </c>
       <c r="C5" s="22" t="inlineStr">
@@ -42292,7 +42292,7 @@
           <t>B | 636呎 (2房)
 $1088万
 $17,108/呎
-(09年-05月)</t>
+(09年-05月-17日)</t>
         </is>
       </c>
       <c r="D5" s="22" t="inlineStr">
@@ -42300,7 +42300,7 @@
           <t>C | 535呎 (2房)
 $3934万
 $73,533/呎
-(13年-10月)</t>
+(13年-10月-24日)</t>
         </is>
       </c>
       <c r="E5" s="22" t="inlineStr">
@@ -42308,7 +42308,7 @@
           <t>D | 551呎 (2房)
 $1411万
 $25,608/呎
-(09年-11月)</t>
+(09年-11月-03日)</t>
         </is>
       </c>
       <c r="F5" s="22" t="inlineStr">
@@ -42316,7 +42316,7 @@
           <t>E | 828呎 (3房)
 $2255万
 $27,229/呎
-(09年-09月)</t>
+(09年-09月-22日)</t>
         </is>
       </c>
       <c r="G5" s="22" t="inlineStr">
@@ -42324,7 +42324,7 @@
           <t>F | 674呎 (2房)
 $1300万
 $19,288/呎
-(09年-06月)</t>
+(09年-06月-02日)</t>
         </is>
       </c>
       <c r="H5" s="22" t="inlineStr">
@@ -42332,7 +42332,7 @@
           <t>G | 677呎 (2房)
 $1466万
 $21,654/呎
-(09年-05月)</t>
+(09年-05月-28日)</t>
         </is>
       </c>
       <c r="I5" s="22" t="inlineStr">
@@ -42340,7 +42340,7 @@
           <t>H | 434呎 (1房)
 $798万
 $18,386/呎
-(09年-08月)</t>
+(09年-08月-20日)</t>
         </is>
       </c>
       <c r="J5" s="22" t="inlineStr">
@@ -42348,7 +42348,7 @@
           <t>J | 530呎 (2房)
 $1894万
 $35,734/呎
-(13年-11月)</t>
+(13年-11月-26日)</t>
         </is>
       </c>
       <c r="K5" s="22" t="inlineStr">
@@ -42356,7 +42356,7 @@
           <t>K | 434呎 (1房)
 $1553万
 $35,789/呎
-(13年-11月)</t>
+(13年-11月-26日)</t>
         </is>
       </c>
     </row>
@@ -42371,7 +42371,7 @@
           <t>A | 640呎 (2房)
 $1093万
 $17,084/呎
-(09年-03月)</t>
+(09年-03月-26日)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -42379,7 +42379,7 @@
           <t>B | 636呎 (2房)
 $1081万
 $16,990/呎
-(09年-04月)</t>
+(09年-04月-29日)</t>
         </is>
       </c>
       <c r="D6" s="22" t="inlineStr">
@@ -42387,7 +42387,7 @@
           <t>C | 535呎 (2房)
 $3934万
 $73,533/呎
-(13年-10月)</t>
+(13年-10月-24日)</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
@@ -42395,7 +42395,7 @@
           <t>D | 551呎 (2房)
 $1307万
 $23,717/呎
-(09年-08月)</t>
+(09年-08月-30日)</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
@@ -42403,7 +42403,7 @@
           <t>E | 828呎 (3房)
 $2107万
 $25,448/呎
-(09年-09月)</t>
+(09年-09月-02日)</t>
         </is>
       </c>
       <c r="G6" s="22" t="inlineStr">
@@ -42411,7 +42411,7 @@
           <t>F | 674呎 (2房)
 $1285万
 $19,061/呎
-(09年-05月)</t>
+(09年-05月-31日)</t>
         </is>
       </c>
       <c r="H6" s="22" t="inlineStr">
@@ -42419,7 +42419,7 @@
           <t>G | 677呎 (2房)
 $1457万
 $21,521/呎
-(09年-05月)</t>
+(09年-05月-28日)</t>
         </is>
       </c>
       <c r="I6" s="22" t="inlineStr">
@@ -42427,7 +42427,7 @@
           <t>H | 434呎 (1房)
 $797万
 $18,359/呎
-(09年-08月)</t>
+(09年-08月-20日)</t>
         </is>
       </c>
       <c r="J6" s="22" t="inlineStr">
@@ -42435,7 +42435,7 @@
           <t>J | 530呎 (2房)
 $1887万
 $35,609/呎
-(13年-11月)</t>
+(13年-11月-26日)</t>
         </is>
       </c>
       <c r="K6" s="22" t="inlineStr">
@@ -42443,7 +42443,7 @@
           <t>K | 434呎 (1房)
 $1548万
 $35,667/呎
-(13年-11月)</t>
+(13年-11月-26日)</t>
         </is>
       </c>
     </row>
@@ -42458,7 +42458,7 @@
           <t>A | 640呎 (2房)
 $1087万
 $16,991/呎
-(09年-04月)</t>
+(09年-04月-01日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -42466,7 +42466,7 @@
           <t>B | 636呎 (2房)
 $1073万
 $16,872/呎
-(09年-04月)</t>
+(09年-04月-29日)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -42474,7 +42474,7 @@
           <t>C | 535呎 (2房)
 $1922万
 $35,926/呎
-(13年-11月)</t>
+(13年-11月-21日)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -42482,7 +42482,7 @@
           <t>D | 551呎 (2房)
 $1379万
 $25,034/呎
-(09年-09月)</t>
+(09年-09月-22日)</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr">
@@ -42490,7 +42490,7 @@
           <t>E | 828呎 (3房)
 $2096万
 $25,314/呎
-(09年-09月)</t>
+(09年-09月-01日)</t>
         </is>
       </c>
       <c r="G7" s="22" t="inlineStr">
@@ -42498,7 +42498,7 @@
           <t>F | 674呎 (2房)
 $1274万
 $18,903/呎
-(09年-05月)</t>
+(09年-05月-25日)</t>
         </is>
       </c>
       <c r="H7" s="22" t="inlineStr">
@@ -42506,7 +42506,7 @@
           <t>G | 677呎 (2房)
 $1448万
 $21,393/呎
-(09年-06月)</t>
+(09年-06月-15日)</t>
         </is>
       </c>
       <c r="I7" s="22" t="inlineStr">
@@ -42514,7 +42514,7 @@
           <t>H | 434呎 (1房)
 $796万
 $18,333/呎
-(09年-08月)</t>
+(09年-08月-20日)</t>
         </is>
       </c>
       <c r="J7" s="22" t="inlineStr">
@@ -42522,7 +42522,7 @@
           <t>J | 530呎 (2房)
 $1881万
 $35,485/呎
-(13年-11月)</t>
+(13年-11月-26日)</t>
         </is>
       </c>
       <c r="K7" s="22" t="inlineStr">
@@ -42530,7 +42530,7 @@
           <t>K | 434呎 (1房)
 $1542万
 $35,540/呎
-(13年-11月)</t>
+(13年-11月-25日)</t>
         </is>
       </c>
     </row>
@@ -42545,7 +42545,7 @@
           <t>A | 640呎 (2房)
 $1087万
 $16,984/呎
-(09年-03月)</t>
+(09年-03月-23日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -42553,7 +42553,7 @@
           <t>B | 641呎 (2房)
 $1060万
 $16,537/呎
-(09年-04月)</t>
+(09年-04月-26日)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -42561,7 +42561,7 @@
           <t>C | 535呎 (2房)
 $1757万
 $32,834/呎
-(13年-11月)</t>
+(13年-11月-10日)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -42569,7 +42569,7 @@
           <t>D | 551呎 (2房)
 $1292万
 $23,453/呎
-(09年-08月)</t>
+(09年-08月-24日)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
@@ -42577,7 +42577,7 @@
           <t>E | 828呎 (3房)
 $2079万
 $25,113/呎
-(09年-09月)</t>
+(09年-09月-01日)</t>
         </is>
       </c>
       <c r="G8" s="22" t="inlineStr">
@@ -42585,7 +42585,7 @@
           <t>F | 674呎 (2房)
 $1267万
 $18,798/呎
-(09年-05月)</t>
+(09年-05月-21日)</t>
         </is>
       </c>
       <c r="H8" s="22" t="inlineStr">
@@ -42593,7 +42593,7 @@
           <t>G | 677呎 (2房)
 $1439万
 $21,261/呎
-(09年-06月)</t>
+(09年-06月-08日)</t>
         </is>
       </c>
       <c r="I8" s="22" t="inlineStr">
@@ -42601,7 +42601,7 @@
           <t>H | 438呎 (1房)
 $3729万
 $85,142/呎
-(13年-10月)</t>
+(13年-10月-24日)</t>
         </is>
       </c>
       <c r="J8" s="22" t="inlineStr">
@@ -42609,7 +42609,7 @@
           <t>J | 530呎 (2房)
 $1828万
 $34,499/呎
-(13年-11月)</t>
+(13年-11月-17日)</t>
         </is>
       </c>
       <c r="K8" s="22" t="inlineStr">
@@ -42617,7 +42617,7 @@
           <t>K | 434呎 (1房)
 $1500万
 $34,552/呎
-(13年-11月)</t>
+(13年-11月-24日)</t>
         </is>
       </c>
     </row>
@@ -42632,7 +42632,7 @@
           <t>A | 640呎 (2房)
 $1087万
 $16,978/呎
-(09年-04月)</t>
+(09年-04月-06日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -42640,7 +42640,7 @@
           <t>B | 636呎 (2房)
 $1058万
 $16,635/呎
-(09年-04月)</t>
+(09年-04月-22日)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -42648,7 +42648,7 @@
           <t>C | 535呎 (2房)
 $1791万
 $33,475/呎
-(13年-11月)</t>
+(13年-11月-07日)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -42656,7 +42656,7 @@
           <t>D | 551呎 (2房)
 $1365万
 $24,771/呎
-(09年-11月)</t>
+(09年-11月-23日)</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
@@ -42664,7 +42664,7 @@
           <t>E | 828呎 (3房)
 $2065万
 $24,939/呎
-(09年-09月)</t>
+(09年-09月-08日)</t>
         </is>
       </c>
       <c r="G9" s="22" t="inlineStr">
@@ -42672,7 +42672,7 @@
           <t>F | 674呎 (2房)
 $1258万
 $18,666/呎
-(09年-05月)</t>
+(09年-05月-25日)</t>
         </is>
       </c>
       <c r="H9" s="22" t="inlineStr">
@@ -42680,7 +42680,7 @@
           <t>G | 677呎 (2房)
 $1386万
 $20,468/呎
-(09年-05月)</t>
+(09年-05月-26日)</t>
         </is>
       </c>
       <c r="I9" s="22" t="inlineStr">
@@ -42688,7 +42688,7 @@
           <t>H | 434呎 (1房)
 $1528万
 $35,216/呎
-(13年-11月)</t>
+(13年-11月-25日)</t>
         </is>
       </c>
       <c r="J9" s="22" t="inlineStr">
@@ -42696,7 +42696,7 @@
           <t>J | 534呎 (2房)
 $3317万
 $62,108/呎
-(13年-10月)</t>
+(13年-10月-24日)</t>
         </is>
       </c>
       <c r="K9" s="22" t="inlineStr">
@@ -42704,7 +42704,7 @@
           <t>K | 435呎 (1房)
 $1296万
 $29,793/呎
-(16年-08月)</t>
+(16年-08月-07日)</t>
         </is>
       </c>
     </row>
@@ -42719,7 +42719,7 @@
           <t>A | 640呎 (2房)
 $1085万
 $16,950/呎
-(09年-04月)</t>
+(09年-04月-02日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -42727,7 +42727,7 @@
           <t>B | 636呎 (2房)
 $1055万
 $16,582/呎
-(09年-04月)</t>
+(09年-04月-29日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -42735,7 +42735,7 @@
           <t>C | 535呎 (2房)
 $1622万
 $30,309/呎
-(13年-11月)</t>
+(13年-11月-07日)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -42743,7 +42743,7 @@
           <t>D | 551呎 (2房)
 $1338万
 $24,275/呎
-(09年-11月)</t>
+(09年-11月-05日)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -42751,7 +42751,7 @@
           <t>E | 828呎 (3房)
 $2049万
 $24,752/呎
-(09年-09月)</t>
+(09年-09月-02日)</t>
         </is>
       </c>
       <c r="G10" s="22" t="inlineStr">
@@ -42759,7 +42759,7 @@
           <t>F | 674呎 (2房)
 $1249万
 $18,535/呎
-(09年-05月)</t>
+(09年-05月-20日)</t>
         </is>
       </c>
       <c r="H10" s="22" t="inlineStr">
@@ -42767,7 +42767,7 @@
           <t>G | 677呎 (2房)
 $1368万
 $20,204/呎
-(09年-05月)</t>
+(09年-05月-31日)</t>
         </is>
       </c>
       <c r="I10" s="22" t="inlineStr">
@@ -42775,7 +42775,7 @@
           <t>H | 434呎 (1房)
 $1269万
 $29,244/呎
-(13年-11月)</t>
+(13年-11月-10日)</t>
         </is>
       </c>
       <c r="J10" s="22" t="inlineStr">
@@ -42783,7 +42783,7 @@
           <t>J | 530呎 (2房)
 $1513万
 $28,548/呎
-(13年-11月)</t>
+(13年-11月-04日)</t>
         </is>
       </c>
       <c r="K10" s="22" t="inlineStr">
@@ -42791,7 +42791,7 @@
           <t>K | 434呎 (1房)
 $1241万
 $28,594/呎
-(13年-11月)</t>
+(13年-11月-04日)</t>
         </is>
       </c>
     </row>
@@ -42806,7 +42806,7 @@
           <t>A | 640呎 (2房)
 $1083万
 $16,924/呎
-(09年-04月)</t>
+(09年-04月-06日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -42814,7 +42814,7 @@
           <t>B | 636呎 (2房)
 $1053万
 $16,556/呎
-(09年-04月)</t>
+(09年-04月-26日)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -42822,7 +42822,7 @@
           <t>C | 535呎 (2房)
 $1619万
 $30,265/呎
-(13年-11月)</t>
+(13年-11月-05日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -42830,7 +42830,7 @@
           <t>D | 551呎 (2房)
 $1329万
 $24,112/呎
-(09年-11月)</t>
+(09年-11月-22日)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -42838,7 +42838,7 @@
           <t>E | 828呎 (3房)
 $2041万
 $24,644/呎
-(09年-09月)</t>
+(09年-09月-08日)</t>
         </is>
       </c>
       <c r="G11" s="22" t="inlineStr">
@@ -42846,7 +42846,7 @@
           <t>F | 674呎 (2房)
 $1240万
 $18,404/呎
-(09年-05月)</t>
+(09年-05月-28日)</t>
         </is>
       </c>
       <c r="H11" s="22" t="inlineStr">
@@ -42854,7 +42854,7 @@
           <t>G | 677呎 (2房)
 $1341万
 $19,808/呎
-(09年-05月)</t>
+(09年-05月-28日)</t>
         </is>
       </c>
       <c r="I11" s="22" t="inlineStr">
@@ -42862,7 +42862,7 @@
           <t>H | 434呎 (1房)
 $1265万
 $29,144/呎
-(13年-11月)</t>
+(13年-11月-03日)</t>
         </is>
       </c>
       <c r="J11" s="22" t="inlineStr">
@@ -42870,7 +42870,7 @@
           <t>J | 530呎 (2房)
 $1508万
 $28,450/呎
-(13年-10月)</t>
+(13年-10月-31日)</t>
         </is>
       </c>
       <c r="K11" s="22" t="inlineStr">
@@ -42878,7 +42878,7 @@
           <t>K | 434呎 (1房)
 $1237万
 $28,493/呎
-(13年-11月)</t>
+(13年-11月-10日)</t>
         </is>
       </c>
     </row>
@@ -42893,7 +42893,7 @@
           <t>A | 640呎 (2房)
 $1081万
 $16,897/呎
-(09年-04月)</t>
+(09年-04月-01日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -42901,7 +42901,7 @@
           <t>B | 636呎 (2房)
 $1051万
 $16,529/呎
-(09年-04月)</t>
+(09年-04月-29日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -42909,7 +42909,7 @@
           <t>C | 535呎 (2房)
 $1617万
 $30,219/呎
-(13年-11月)</t>
+(13年-11月-06日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -42917,7 +42917,7 @@
           <t>D | 551呎 (2房)
 $1321万
 $23,980/呎
-(09年-10月)</t>
+(09年-10月-11日)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -42925,7 +42925,7 @@
           <t>E | 828呎 (3房)
 $2129万
 $25,716/呎
-(09年-09月)</t>
+(09年-09月-21日)</t>
         </is>
       </c>
       <c r="G12" s="22" t="inlineStr">
@@ -42933,7 +42933,7 @@
           <t>F | 674呎 (2房)
 $1236万
 $18,338/呎
-(09年-05月)</t>
+(09年-05月-21日)</t>
         </is>
       </c>
       <c r="H12" s="22" t="inlineStr">
@@ -42941,7 +42941,7 @@
           <t>G | 677呎 (2房)
 $1336万
 $19,729/呎
-(09年-06月)</t>
+(09年-06月-03日)</t>
         </is>
       </c>
       <c r="I12" s="22" t="inlineStr">
@@ -42949,7 +42949,7 @@
           <t>H | 434呎 (1房)
 $1260万
 $29,041/呎
-(13年-11月)</t>
+(13年-11月-11日)</t>
         </is>
       </c>
       <c r="J12" s="22" t="inlineStr">
@@ -42957,7 +42957,7 @@
           <t>J | 530呎 (2房)
 $1503万
 $28,349/呎
-(13年-11月)</t>
+(13年-11月-06日)</t>
         </is>
       </c>
       <c r="K12" s="22" t="inlineStr">
@@ -42965,7 +42965,7 @@
           <t>K | 435呎 (1房)
 $1232万
 $28,330/呎
-(13年-11月)</t>
+(13年-11月-06日)</t>
         </is>
       </c>
     </row>
@@ -42980,7 +42980,7 @@
           <t>A | 659呎 (2房)
 $1080万
 $16,384/呎
-(09年-04月)</t>
+(09年-04月-06日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -42988,7 +42988,7 @@
           <t>B | 636呎 (2房)
 $1050万
 $16,503/呎
-(09年-04月)</t>
+(09年-04月-29日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -42996,7 +42996,7 @@
           <t>C | 535呎 (2房)
 $1282万
 $23,955/呎
-(09年-09月)</t>
+(09年-09月-06日)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -43004,7 +43004,7 @@
           <t>D | 551呎 (2房)
 $1227万
 $22,268/呎
-(09年-08月)</t>
+(09年-08月-31日)</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -43012,7 +43012,7 @@
           <t>E | 828呎 (3房)
 $2127万
 $25,689/呎
-(09年-10月)</t>
+(09年-10月-06日)</t>
         </is>
       </c>
       <c r="G13" s="22" t="inlineStr">
@@ -43020,7 +43020,7 @@
           <t>F | 674呎 (2房)
 $1234万
 $18,312/呎
-(09年-05月)</t>
+(09年-05月-28日)</t>
         </is>
       </c>
       <c r="H13" s="22" t="inlineStr">
@@ -43028,7 +43028,7 @@
           <t>G | 677呎 (2房)
 $1335万
 $19,716/呎
-(09年-05月)</t>
+(09年-05月-28日)</t>
         </is>
       </c>
       <c r="I13" s="22" t="inlineStr">
@@ -43036,7 +43036,7 @@
           <t>H | 434呎 (1房)
 $1526万
 $35,163/呎
-(13年-11月)</t>
+(13年-11月-21日)</t>
         </is>
       </c>
       <c r="J13" s="22" t="inlineStr">
@@ -43044,7 +43044,7 @@
           <t>J | 530呎 (2房)
 $1819万
 $34,325/呎
-(13年-11月)</t>
+(13年-11月-21日)</t>
         </is>
       </c>
       <c r="K13" s="22" t="inlineStr">
@@ -43052,7 +43052,7 @@
           <t>K | 434呎 (1房)
 $1492万
 $34,379/呎
-(13年-11月)</t>
+(13年-11月-26日)</t>
         </is>
       </c>
     </row>
@@ -43067,7 +43067,7 @@
           <t>A | 640呎 (2房)
 $1078万
 $16,843/呎
-(09年-05月)</t>
+(09年-05月-03日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -43075,7 +43075,7 @@
           <t>B | 636呎 (2房)
 $1048万
 $16,477/呎
-(09年-04月)</t>
+(09年-04月-26日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -43083,7 +43083,7 @@
           <t>C | 535呎 (2房)
 $1905万
 $35,606/呎
-(13年-11月)</t>
+(13年-11月-18日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -43091,7 +43091,7 @@
           <t>D | 551呎 (2房)
 $1220万
 $22,136/呎
-(09年-08月)</t>
+(09年-08月-30日)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -43099,7 +43099,7 @@
           <t>E | 828呎 (3房)
 $2163万
 $26,118/呎
-(09年-12月)</t>
+(09年-12月-17日)</t>
         </is>
       </c>
       <c r="G14" s="22" t="inlineStr">
@@ -43107,7 +43107,7 @@
           <t>F | 674呎 (2房)
 $1233万
 $18,299/呎
-(09年-06月)</t>
+(09年-06月-08日)</t>
         </is>
       </c>
       <c r="H14" s="22" t="inlineStr">
@@ -43115,7 +43115,7 @@
           <t>G | 677呎 (2房)
 $1334万
 $19,702/呎
-(09年-06月)</t>
+(09年-06月-08日)</t>
         </is>
       </c>
       <c r="I14" s="22" t="inlineStr">
@@ -43123,7 +43123,7 @@
           <t>H | 434呎 (1房)
 $1552万
 $35,761/呎
-(13年-11月)</t>
+(13年-11月-25日)</t>
         </is>
       </c>
       <c r="J14" s="22" t="inlineStr">
@@ -43131,7 +43131,7 @@
           <t>J | 530呎 (2房)
 $1850万
 $34,908/呎
-(13年-11月)</t>
+(13年-11月-27日)</t>
         </is>
       </c>
       <c r="K14" s="22" t="inlineStr">
@@ -43139,7 +43139,7 @@
           <t>K | 434呎 (1房)
 $1518万
 $34,966/呎
-(13年-11月)</t>
+(13年-11月-27日)</t>
         </is>
       </c>
     </row>
@@ -43154,7 +43154,7 @@
           <t>A | 667呎 (2房)
 $1080万
 $16,192/呎
-(09年-04月)</t>
+(09年-04月-20日)</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr"/>
@@ -43163,7 +43163,7 @@
           <t>C | 546呎 (2房)
 $1905万
 $34,884/呎
-(13年-11月)</t>
+(13年-11月-21日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -43171,7 +43171,7 @@
           <t>D | 551呎 (2房)
 $1303万
 $23,651/呎
-(09年-12月)</t>
+(09年-12月-02日)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -43179,7 +43179,7 @@
           <t>E | 828呎 (3房)
 $2107万
 $25,448/呎
-(09年-09月)</t>
+(09年-09月-08日)</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -43187,7 +43187,7 @@
           <t>F | 674呎 (2房)
 $1232万
 $18,272/呎
-(09年-06月)</t>
+(09年-06月-15日)</t>
         </is>
       </c>
       <c r="H15" s="22" t="inlineStr">
@@ -43195,7 +43195,7 @@
           <t>G | 677呎 (2房)
 $1332万
 $19,676/呎
-(09年-06月)</t>
+(09年-06月-15日)</t>
         </is>
       </c>
       <c r="I15" s="22" t="inlineStr">
@@ -43203,7 +43203,7 @@
           <t>H | 434呎 (1房)
 $1547万
 $35,636/呎
-(13年-11月)</t>
+(13年-11月-26日)</t>
         </is>
       </c>
       <c r="J15" s="22" t="inlineStr">
@@ -43211,7 +43211,7 @@
           <t>J | 530呎 (2房)
 $1882万
 $35,518/呎
-(13年-11月)</t>
+(13年-11月-26日)</t>
         </is>
       </c>
       <c r="K15" s="22" t="inlineStr">
@@ -43219,7 +43219,7 @@
           <t>K | 434呎 (1房)
 $1512万
 $34,844/呎
-(13年-11月)</t>
+(13年-11月-26日)</t>
         </is>
       </c>
     </row>
@@ -43234,7 +43234,7 @@
           <t>A | 637呎 (2房)
 $1078万
 $16,915/呎
-(09年-03月)</t>
+(09年-03月-26日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -43242,7 +43242,7 @@
           <t>B | 641呎 (2房)
 $1048万
 $16,348/呎
-(09年-04月)</t>
+(09年-04月-28日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -43250,7 +43250,7 @@
           <t>C | 531呎 (2房)
 $1896万
 $35,715/呎
-(13年-11月)</t>
+(13年-11月-18日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -43258,7 +43258,7 @@
           <t>D | 555呎 (2房)
 $1227万
 $22,103/呎
-(09年-08月)</t>
+(09年-08月-26日)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -43266,7 +43266,7 @@
           <t>E | 831呎 (3房)
 $2920万
 $35,144/呎
-(13年-11月)</t>
+(13年-11月-26日)</t>
         </is>
       </c>
       <c r="G16" s="21" t="inlineStr"/>
@@ -43286,7 +43286,7 @@
           <t>A | 660呎 (2房)
 $1078万
 $16,326/呎
-(09年-03月)</t>
+(09年-03月-26日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -43294,7 +43294,7 @@
           <t>B | 635呎 (2房)
 $1048万
 $16,503/呎
-(09年-04月)</t>
+(09年-04月-29日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -43302,7 +43302,7 @@
           <t>C | 531呎 (2房)
 $1778万
 $33,475/呎
-(12年-07月)</t>
+(12年-07月-04日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -43310,7 +43310,7 @@
           <t>D | 555呎 (2房)
 $1226万
 $22,090/呎
-(09年-08月)</t>
+(09年-08月-31日)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -43318,7 +43318,7 @@
           <t>E | 831呎 (3房)
 $2244万
 $27,004/呎
-(10年-01月)</t>
+(10年-01月-21日)</t>
         </is>
       </c>
       <c r="G17" s="21" t="inlineStr"/>
@@ -43338,7 +43338,7 @@
           <t>A | 637呎 (2房)
 $1078万
 $16,915/呎
-(09年-03月)</t>
+(09年-03月-25日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -43346,7 +43346,7 @@
           <t>B | 635呎 (2房)
 $1048万
 $16,503/呎
-(09年-04月)</t>
+(09年-04月-29日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -43354,7 +43354,7 @@
           <t>C | 531呎 (2房)
 $1778万
 $33,475/呎
-(12年-09月)</t>
+(12年-09月-19日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -43362,7 +43362,7 @@
           <t>D | 555呎 (2房)
 $1225万
 $22,077/呎
-(09年-09月)</t>
+(09年-09月-07日)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -43370,7 +43370,7 @@
           <t>E | 831呎 (3房)
 $1952万
 $23,493/呎
-(09年-08月)</t>
+(09年-08月-25日)</t>
         </is>
       </c>
       <c r="G18" s="21" t="inlineStr"/>
@@ -43390,7 +43390,7 @@
           <t>A | 637呎 (2房)
 $1073万
 $16,848/呎
-(09年-04月)</t>
+(09年-04月-26日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -43398,7 +43398,7 @@
           <t>B | 635呎 (2房)
 $1046万
 $16,476/呎
-(09年-05月)</t>
+(09年-05月-18日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -43406,7 +43406,7 @@
           <t>C | 531呎 (2房)
 $1778万
 $33,475/呎
-(12年-10月)</t>
+(12年-10月-21日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -43414,7 +43414,7 @@
           <t>D | 555呎 (2房)
 $1312万
 $23,635/呎
-(09年-09月)</t>
+(09年-09月-22日)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -43422,7 +43422,7 @@
           <t>E | 831呎 (3房)
 $2076万
 $24,978/呎
-(09年-10月)</t>
+(09年-10月-06日)</t>
         </is>
       </c>
       <c r="G19" s="21" t="inlineStr"/>
@@ -43442,7 +43442,7 @@
           <t>A | 637呎 (2房)
 $1065万
 $16,712/呎
-(09年-03月)</t>
+(09年-03月-22日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -43450,7 +43450,7 @@
           <t>B | 635呎 (2房)
 $1043万
 $16,424/呎
-(09年-05月)</t>
+(09年-05月-12日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -43458,7 +43458,7 @@
           <t>C | 531呎 (2房)
 $1778万
 $33,475/呎
-(12年-10月)</t>
+(12年-10月-24日)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -43466,7 +43466,7 @@
           <t>D | 555呎 (2房)
 $1205万
 $21,704/呎
-(09年-08月)</t>
+(09年-08月-31日)</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -43474,7 +43474,7 @@
           <t>E | 831呎 (3房)
 $2011万
 $24,204/呎
-(09年-09月)</t>
+(09年-09月-06日)</t>
         </is>
       </c>
       <c r="G20" s="21" t="inlineStr"/>
@@ -43494,7 +43494,7 @@
           <t>A | 637呎 (2房)
 $1063万
 $16,685/呎
-(09年-04月)</t>
+(09年-04月-22日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -43502,7 +43502,7 @@
           <t>B | 641呎 (2房)
 $1043万
 $16,270/呎
-(09年-05月)</t>
+(09年-05月-13日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -43510,7 +43510,7 @@
           <t>C | 531呎 (2房)
 $1778万
 $33,475/呎
-(12年-11月)</t>
+(12年-11月-11日)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -43518,7 +43518,7 @@
           <t>D | 555呎 (2房)
 $1203万
 $21,677/呎
-(09年-09月)</t>
+(09年-09月-22日)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -43526,7 +43526,7 @@
           <t>E | 831呎 (3房)
 $1907万
 $22,953/呎
-(09年-09月)</t>
+(09年-09月-02日)</t>
         </is>
       </c>
       <c r="G21" s="21" t="inlineStr"/>
@@ -43546,7 +43546,7 @@
           <t>A | 637呎 (2房)
 $1062万
 $16,672/呎
-(09年-04月)</t>
+(09年-04月-26日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -43554,7 +43554,7 @@
           <t>B | 635呎 (2房)
 $1042万
 $16,411/呎
-(09年-05月)</t>
+(09年-05月-25日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -43562,7 +43562,7 @@
           <t>C | 531呎 (2房)
 $1778万
 $33,475/呎
-(12年-12月)</t>
+(12年-12月-27日)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -43570,7 +43570,7 @@
           <t>D | 555呎 (2房)
 $1304万
 $23,502/呎
-(09年-09月)</t>
+(09年-09月-07日)</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -43578,7 +43578,7 @@
           <t>E | 831呎 (3房)
 $1894万
 $22,791/呎
-(09年-09月)</t>
+(09年-09月-07日)</t>
         </is>
       </c>
       <c r="G22" s="21" t="inlineStr"/>
@@ -43598,7 +43598,7 @@
           <t>A | 637呎 (2房)
 $1060万
 $16,645/呎
-(09年-04月)</t>
+(09年-04月-26日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -43606,7 +43606,7 @@
           <t>B | 635呎 (2房)
 $1041万
 $16,397/呎
-(09年-05月)</t>
+(09年-05月-21日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -43614,7 +43614,7 @@
           <t>C | 531呎 (2房)
 $1778万
 $33,475/呎
-(13年-01月)</t>
+(13年-01月-31日)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -43622,7 +43622,7 @@
           <t>D | 555呎 (2房)
 $1202万
 $21,651/呎
-(09年-09月)</t>
+(09年-09月-01日)</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -43630,7 +43630,7 @@
           <t>E | 831呎 (3房)
 $1851万
 $22,278/呎
-(09年-09月)</t>
+(09年-09月-09日)</t>
         </is>
       </c>
       <c r="G23" s="21" t="inlineStr"/>
@@ -43650,7 +43650,7 @@
           <t>A | 637呎 (2房)
 $1060万
 $16,645/呎
-(09年-04月)</t>
+(09年-04月-14日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -43658,7 +43658,7 @@
           <t>B | 635呎 (2房)
 $1040万
 $16,384/呎
-(09年-05月)</t>
+(09年-05月-14日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -43666,7 +43666,7 @@
           <t>C | 531呎 (2房)
 $1671万
 $31,466/呎
-(11年-06月)</t>
+(11年-06月-01日)</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -43674,7 +43674,7 @@
           <t>D | 555呎 (2房)
 $1201万
 $21,637/呎
-(09年-08月)</t>
+(09年-08月-24日)</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -43682,7 +43682,7 @@
           <t>E | 831呎 (3房)
 $1851万
 $22,278/呎
-(09年-09月)</t>
+(09年-09月-08日)</t>
         </is>
       </c>
       <c r="G24" s="21" t="inlineStr"/>
@@ -43702,7 +43702,7 @@
           <t>A | 637呎 (2房)
 $1060万
 $16,641/呎
-(09年-04月)</t>
+(09年-04月-22日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -43710,7 +43710,7 @@
           <t>B | 635呎 (2房)
 $1040万
 $16,384/呎
-(09年-05月)</t>
+(09年-05月-18日)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -43718,7 +43718,7 @@
           <t>C | 531呎 (2房)
 $1621万
 $30,529/呎
-(11年-03月)</t>
+(11年-03月-23日)</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
@@ -43726,7 +43726,7 @@
           <t>D | 555呎 (2房)
 $1201万
 $21,637/呎
-(09年-09月)</t>
+(09年-09月-15日)</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -43734,7 +43734,7 @@
           <t>E | 831呎 (3房)
 $2025万
 $24,371/呎
-(09年-09月)</t>
+(09年-09月-06日)</t>
         </is>
       </c>
       <c r="G25" s="21" t="inlineStr"/>
@@ -43754,7 +43754,7 @@
           <t>A | 637呎 (2房)
 $1062万
 $16,670/呎
-(09年-04月)</t>
+(09年-04月-15日)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -43762,7 +43762,7 @@
           <t>B | 635呎 (2房)
 $1040万
 $16,371/呎
-(09年-05月)</t>
+(09年-05月-20日)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -43770,7 +43770,7 @@
           <t>C | 531呎 (2房)
 $1529万
 $28,788/呎
-(11年-03月)</t>
+(11年-03月-14日)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -43778,7 +43778,7 @@
           <t>D | 555呎 (2房)
 $1290万
 $23,235/呎
-(09年-09月)</t>
+(09年-09月-03日)</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
@@ -43786,7 +43786,7 @@
           <t>E | 831呎 (3房)
 $1849万
 $22,251/呎
-(09年-08月)</t>
+(09年-08月-24日)</t>
         </is>
       </c>
       <c r="G26" s="21" t="inlineStr"/>
@@ -43806,7 +43806,7 @@
           <t>A | 637呎 (2房)
 $1061万
 $16,656/呎
-(09年-04月)</t>
+(09年-04月-22日)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -43814,7 +43814,7 @@
           <t>B | 641呎 (2房)
 $1039万
 $16,205/呎
-(09年-05月)</t>
+(09年-05月-18日)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -43822,7 +43822,7 @@
           <t>C | 531呎 (2房)
 $1493万
 $28,119/呎
-(11年-01月)</t>
+(11年-01月-16日)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -43830,7 +43830,7 @@
           <t>D | 555呎 (2房)
 $1196万
 $21,544/呎
-(09年-09月)</t>
+(09年-09月-01日)</t>
         </is>
       </c>
       <c r="F27" s="22" t="inlineStr">
@@ -43838,7 +43838,7 @@
           <t>E | 831呎 (3房)
 $1848万
 $22,238/呎
-(09年-09月)</t>
+(09年-09月-08日)</t>
         </is>
       </c>
       <c r="G27" s="21" t="inlineStr"/>
@@ -43858,7 +43858,7 @@
           <t>A | 637呎 (2房)
 $1060万
 $16,643/呎
-(09年-04月)</t>
+(09年-04月-16日)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -43866,7 +43866,7 @@
           <t>B | 635呎 (2房)
 $1038万
 $16,345/呎
-(09年-05月)</t>
+(09年-05月-19日)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -43874,7 +43874,7 @@
           <t>C | 531呎 (2房)
 $1422万
 $26,780/呎
-(10年-05月)</t>
+(10年-05月-16日)</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
@@ -43882,7 +43882,7 @@
           <t>D | 555呎 (2房)
 $1195万
 $21,531/呎
-(09年-08月)</t>
+(09年-08月-31日)</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
@@ -43890,7 +43890,7 @@
           <t>E | 831呎 (3房)
 $1847万
 $22,224/呎
-(09年-09月)</t>
+(09年-09月-08日)</t>
         </is>
       </c>
       <c r="G28" s="21" t="inlineStr"/>
@@ -43910,7 +43910,7 @@
           <t>A | 661呎 (2房)
 $1059万
 $16,025/呎
-(09年-04月)</t>
+(09年-04月-27日)</t>
         </is>
       </c>
       <c r="C29" s="22" t="inlineStr">
@@ -43918,7 +43918,7 @@
           <t>B | 635呎 (2房)
 $1037万
 $16,331/呎
-(09年-06月)</t>
+(09年-06月-01日)</t>
         </is>
       </c>
       <c r="D29" s="22" t="inlineStr">
@@ -43926,7 +43926,7 @@
           <t>C | 531呎 (2房)
 $1422万
 $26,780/呎
-(10年-06月)</t>
+(10年-06月-09日)</t>
         </is>
       </c>
       <c r="E29" s="22" t="inlineStr">
@@ -43934,7 +43934,7 @@
           <t>D | 555呎 (2房)
 $1194万
 $21,518/呎
-(09年-09月)</t>
+(09年-09月-15日)</t>
         </is>
       </c>
       <c r="F29" s="22" t="inlineStr">
@@ -43942,7 +43942,7 @@
           <t>E | 831呎 (3房)
 $1846万
 $22,210/呎
-(09年-09月)</t>
+(09年-09月-10日)</t>
         </is>
       </c>
       <c r="G29" s="21" t="inlineStr"/>
@@ -43962,7 +43962,7 @@
           <t>A | 637呎 (2房)
 $1058万
 $16,615/呎
-(09年-04月)</t>
+(09年-04月-23日)</t>
         </is>
       </c>
       <c r="C30" s="22" t="inlineStr">
@@ -43970,7 +43970,7 @@
           <t>B | 635呎 (2房)
 $1036万
 $16,318/呎
-(09年-06月)</t>
+(09年-06月-02日)</t>
         </is>
       </c>
       <c r="D30" s="22" t="inlineStr">
@@ -43978,7 +43978,7 @@
           <t>C | 531呎 (2房)
 $1386万
 $26,110/呎
-(10年-01月)</t>
+(10年-01月-26日)</t>
         </is>
       </c>
       <c r="E30" s="22" t="inlineStr">
@@ -43986,7 +43986,7 @@
           <t>D | 555呎 (2房)
 $1282万
 $23,102/呎
-(09年-09月)</t>
+(09年-09月-07日)</t>
         </is>
       </c>
       <c r="F30" s="22" t="inlineStr">
@@ -43994,7 +43994,7 @@
           <t>E | 831呎 (3房)
 $1980万
 $23,827/呎
-(10年-01月)</t>
+(10年-01月-07日)</t>
         </is>
       </c>
       <c r="G30" s="21" t="inlineStr"/>
@@ -44014,7 +44014,7 @@
           <t>A | 637呎 (2房)
 $1058万
 $16,602/呎
-(09年-04月)</t>
+(09年-04月-26日)</t>
         </is>
       </c>
       <c r="C31" s="22" t="inlineStr">
@@ -44022,7 +44022,7 @@
           <t>B | 635呎 (2房)
 $1035万
 $16,305/呎
-(09年-05月)</t>
+(09年-05月-18日)</t>
         </is>
       </c>
       <c r="D31" s="22" t="inlineStr">
@@ -44030,7 +44030,7 @@
           <t>C | 531呎 (2房)
 $1422万
 $26,780/呎
-(10年-07月)</t>
+(10年-07月-29日)</t>
         </is>
       </c>
       <c r="E31" s="22" t="inlineStr">
@@ -44038,7 +44038,7 @@
           <t>D | 555呎 (2房)
 $1193万
 $21,491/呎
-(09年-09月)</t>
+(09年-09月-08日)</t>
         </is>
       </c>
       <c r="F31" s="22" t="inlineStr">
@@ -44046,7 +44046,7 @@
           <t>E | 831呎 (3房)
 $2244万
 $27,004/呎
-(10年-01月)</t>
+(10年-01月-17日)</t>
         </is>
       </c>
       <c r="G31" s="21" t="inlineStr"/>
@@ -44066,7 +44066,7 @@
           <t>A | 637呎 (2房)
 $1057万
 $16,588/呎
-(09年-04月)</t>
+(09年-04月-27日)</t>
         </is>
       </c>
       <c r="C32" s="22" t="inlineStr">
@@ -44074,7 +44074,7 @@
           <t>B | 635呎 (2房)
 $1035万
 $16,292/呎
-(09年-05月)</t>
+(09年-05月-18日)</t>
         </is>
       </c>
       <c r="D32" s="22" t="inlineStr">
@@ -44082,7 +44082,7 @@
           <t>C | 531呎 (2房)
 $1422万
 $26,780/呎
-(10年-11月)</t>
+(10年-11月-25日)</t>
         </is>
       </c>
       <c r="E32" s="22" t="inlineStr">
@@ -44090,7 +44090,7 @@
           <t>D | 555呎 (2房)
 $1192万
 $21,478/呎
-(09年-08月)</t>
+(09年-08月-26日)</t>
         </is>
       </c>
       <c r="F32" s="22" t="inlineStr">
@@ -44098,7 +44098,7 @@
           <t>E | 831呎 (3房)
 $2300万
 $27,677/呎
-(10年-04月)</t>
+(10年-04月-22日)</t>
         </is>
       </c>
       <c r="G32" s="21" t="inlineStr"/>
@@ -44118,7 +44118,7 @@
           <t>A | 637呎 (2房)
 $1056万
 $16,575/呎
-(09年-04月)</t>
+(09年-04月-26日)</t>
         </is>
       </c>
       <c r="C33" s="22" t="inlineStr">
@@ -44126,7 +44126,7 @@
           <t>B | 635呎 (2房)
 $1034万
 $16,279/呎
-(09年-05月)</t>
+(09年-05月-21日)</t>
         </is>
       </c>
       <c r="D33" s="22" t="inlineStr">
@@ -44134,7 +44134,7 @@
           <t>C | 531呎 (2房)
 $1422万
 $26,780/呎
-(10年-11月)</t>
+(10年-11月-30日)</t>
         </is>
       </c>
       <c r="E33" s="22" t="inlineStr">
@@ -44142,7 +44142,7 @@
           <t>D | 555呎 (2房)
 $1192万
 $21,478/呎
-(09年-09月)</t>
+(09年-09月-08日)</t>
         </is>
       </c>
       <c r="F33" s="22" t="inlineStr">
@@ -44150,7 +44150,7 @@
           <t>E | 831呎 (3房)
 $1950万
 $23,466/呎
-(09年-09月)</t>
+(09年-09月-22日)</t>
         </is>
       </c>
       <c r="G33" s="21" t="inlineStr"/>
@@ -44170,7 +44170,7 @@
           <t>A | 637呎 (2房)
 $1056万
 $16,575/呎
-(09年-04月)</t>
+(09年-04月-28日)</t>
         </is>
       </c>
       <c r="C34" s="22" t="inlineStr">
@@ -44178,7 +44178,7 @@
           <t>B | 635呎 (2房)
 $1034万
 $16,279/呎
-(09年-05月)</t>
+(09年-05月-20日)</t>
         </is>
       </c>
       <c r="D34" s="22" t="inlineStr">
@@ -44186,7 +44186,7 @@
           <t>C | 544呎 (2房)
 $1422万
 $26,140/呎
-(11年-02月)</t>
+(11年-02月-08日)</t>
         </is>
       </c>
       <c r="E34" s="22" t="inlineStr">
@@ -44194,7 +44194,7 @@
           <t>D | 555呎 (2房)
 $1329万
 $23,941/呎
-(09年-12月)</t>
+(09年-12月-15日)</t>
         </is>
       </c>
       <c r="F34" s="22" t="inlineStr">
@@ -44202,7 +44202,7 @@
           <t>E | 831呎 (3房)
 $1840万
 $22,143/呎
-(09年-08月)</t>
+(09年-08月-26日)</t>
         </is>
       </c>
       <c r="G34" s="21" t="inlineStr"/>
@@ -44222,7 +44222,7 @@
           <t>A | 637呎 (2房)
 $1055万
 $16,561/呎
-(09年-04月)</t>
+(09年-04月-26日)</t>
         </is>
       </c>
       <c r="C35" s="22" t="inlineStr">
@@ -44230,7 +44230,7 @@
           <t>B | 635呎 (2房)
 $1033万
 $16,266/呎
-(09年-05月)</t>
+(09年-05月-25日)</t>
         </is>
       </c>
       <c r="D35" s="22" t="inlineStr">
@@ -44238,7 +44238,7 @@
           <t>C | 531呎 (2房)
 $1458万
 $27,449/呎
-(11年-03月)</t>
+(11年-03月-24日)</t>
         </is>
       </c>
       <c r="E35" s="22" t="inlineStr">
@@ -44246,7 +44246,7 @@
           <t>D | 555呎 (2房)
 $1190万
 $21,438/呎
-(09年-09月)</t>
+(09年-09月-08日)</t>
         </is>
       </c>
       <c r="F35" s="22" t="inlineStr">
@@ -44254,7 +44254,7 @@
           <t>E | 842呎 (3房)
 $2300万
 $27,317/呎
-(10年-11月)</t>
+(10年-11月-22日)</t>
         </is>
       </c>
       <c r="G35" s="21" t="inlineStr"/>
@@ -44274,7 +44274,7 @@
           <t>A | 637呎 (2房)
 $1054万
 $16,548/呎
-(09年-05月)</t>
+(09年-05月-05日)</t>
         </is>
       </c>
       <c r="C36" s="22" t="inlineStr">
@@ -44282,7 +44282,7 @@
           <t>B | 635呎 (2房)
 $1032万
 $16,252/呎
-(09年-06月)</t>
+(09年-06月-08日)</t>
         </is>
       </c>
       <c r="D36" s="22" t="inlineStr">
@@ -44290,7 +44290,7 @@
           <t>C | 531呎 (2房)
 $1493万
 $28,119/呎
-(11年-03月)</t>
+(11年-03月-15日)</t>
         </is>
       </c>
       <c r="E36" s="22" t="inlineStr">
@@ -44298,7 +44298,7 @@
           <t>D | 555呎 (2房)
 $1260万
 $22,703/呎
-(09年-09月)</t>
+(09年-09月-02日)</t>
         </is>
       </c>
       <c r="F36" s="22" t="inlineStr">
@@ -44306,7 +44306,7 @@
           <t>E | 831呎 (3房)
 $2300万
 $27,679/呎
-(10年-11月)</t>
+(10年-11月-16日)</t>
         </is>
       </c>
       <c r="G36" s="21" t="inlineStr"/>
@@ -44326,7 +44326,7 @@
           <t>A | 637呎 (2房)
 $1054万
 $16,548/呎
-(09年-04月)</t>
+(09年-04月-29日)</t>
         </is>
       </c>
       <c r="C37" s="22" t="inlineStr">
@@ -44334,7 +44334,7 @@
           <t>B | 635呎 (2房)
 $1032万
 $16,252/呎
-(09年-05月)</t>
+(09年-05月-28日)</t>
         </is>
       </c>
       <c r="D37" s="22" t="inlineStr">
@@ -44342,7 +44342,7 @@
           <t>C | 544呎 (2房)
 $1600万
 $29,407/呎
-(11年-04月)</t>
+(11年-04月-27日)</t>
         </is>
       </c>
       <c r="E37" s="22" t="inlineStr">
@@ -44350,7 +44350,7 @@
           <t>D | 555呎 (2房)
 $1256万
 $22,636/呎
-(09年-09月)</t>
+(09年-09月-06日)</t>
         </is>
       </c>
       <c r="F37" s="22" t="inlineStr">
@@ -44358,7 +44358,7 @@
           <t>E | 831呎 (3房)
 $2300万
 $27,679/呎
-(10年-12月)</t>
+(10年-12月-12日)</t>
         </is>
       </c>
       <c r="G37" s="21" t="inlineStr"/>
@@ -44501,7 +44501,7 @@
           <t>A | 1377呎 (4+房)
 $2858万
 $20,756/呎
-(09年-03月)</t>
+(09年-03月-24日)</t>
         </is>
       </c>
       <c r="C5" s="22" t="inlineStr">
@@ -44509,7 +44509,7 @@
           <t>B | 1281呎 (4+房)
 $2607万
 $20,351/呎
-(09年-03月)</t>
+(09年-03月-12日)</t>
         </is>
       </c>
       <c r="D5" s="22" t="inlineStr">
@@ -44517,7 +44517,7 @@
           <t>C | 1008呎 (3房)
 $2102万
 $20,855/呎
-(09年-03月)</t>
+(09年-03月-15日)</t>
         </is>
       </c>
       <c r="E5" s="22" t="inlineStr">
@@ -44525,7 +44525,7 @@
           <t>D | 875呎 (3房)
 $1650万
 $18,853/呎
-(09年-03月)</t>
+(09年-03月-15日)</t>
         </is>
       </c>
     </row>
@@ -44540,7 +44540,7 @@
           <t>A | 1401呎 (4+房)
 $2802万
 $20,000/呎
-(09年-03月)</t>
+(09年-03月-22日)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -44548,7 +44548,7 @@
           <t>B | 1281呎 (4+房)
 $2590万
 $20,216/呎
-(09年-03月)</t>
+(09年-03月-18日)</t>
         </is>
       </c>
       <c r="D6" s="22" t="inlineStr">
@@ -44556,7 +44556,7 @@
           <t>C | 1008呎 (3房)
 $2051万
 $20,351/呎
-(09年-03月)</t>
+(09年-03月-22日)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
@@ -44579,7 +44579,7 @@
           <t>A | 1377呎 (4+房)
 $2765万
 $20,077/呎
-(09年-03月)</t>
+(09年-03月-08日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -44587,7 +44587,7 @@
           <t>B | 1281呎 (4+房)
 $2572万
 $20,080/呎
-(09年-03月)</t>
+(09年-03月-12日)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -44595,7 +44595,7 @@
           <t>C | 1008呎 (3房)
 $2047万
 $20,310/呎
-(09年-03月)</t>
+(09年-03月-12日)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -44603,7 +44603,7 @@
           <t>D | 875呎 (3房)
 $1648万
 $18,840/呎
-(09年-03月)</t>
+(09年-03月-12日)</t>
         </is>
       </c>
     </row>
@@ -44618,7 +44618,7 @@
           <t>A | 1401呎 (4+房)
 $2760万
 $19,700/呎
-(09年-03月)</t>
+(09年-03月-17日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -44626,7 +44626,7 @@
           <t>B | 1281呎 (4+房)
 $2546万
 $19,876/呎
-(09年-03月)</t>
+(09年-03月-17日)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -44634,7 +44634,7 @@
           <t>C | 1008呎 (3房)
 $2046万
 $20,297/呎
-(09年-03月)</t>
+(09年-03月-22日)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -44642,7 +44642,7 @@
           <t>D | 875呎 (3房)
 $1647万
 $18,826/呎
-(09年-03月)</t>
+(09年-03月-17日)</t>
         </is>
       </c>
     </row>
@@ -44657,7 +44657,7 @@
           <t>A | 1377呎 (4+房)
 $2746万
 $19,942/呎
-(09年-03月)</t>
+(09年-03月-24日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -44665,7 +44665,7 @@
           <t>B | 1281呎 (4+房)
 $2534万
 $19,781/呎
-(09年-03月)</t>
+(09年-03月-15日)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -44673,7 +44673,7 @@
           <t>C | 1008呎 (3房)
 $2031万
 $20,147/呎
-(09年-03月)</t>
+(09年-03月-17日)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -44681,7 +44681,7 @@
           <t>D | 875呎 (3房)
 $1647万
 $18,826/呎
-(09年-03月)</t>
+(09年-03月-17日)</t>
         </is>
       </c>
     </row>
@@ -44696,7 +44696,7 @@
           <t>A | 1377呎 (4+房)
 $2737万
 $19,874/呎
-(09年-03月)</t>
+(09年-03月-22日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -44704,7 +44704,7 @@
           <t>B | 1281呎 (4+房)
 $2510万
 $19,594/呎
-(09年-03月)</t>
+(09年-03月-17日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -44712,7 +44712,7 @@
           <t>C | 1008呎 (3房)
 $2020万
 $20,038/呎
-(09年-03月)</t>
+(09年-03月-17日)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -44720,7 +44720,7 @@
           <t>D | 910呎 (3房)
 $1645万
 $18,075/呎
-(09年-03月)</t>
+(09年-03月-17日)</t>
         </is>
       </c>
     </row>
@@ -44735,7 +44735,7 @@
           <t>A | 1377呎 (4+房)
 $2727万
 $19,806/呎
-(09年-03月)</t>
+(09年-03月-25日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -44743,7 +44743,7 @@
           <t>B | 1281呎 (4+房)
 $2499万
 $19,510/呎
-(09年-03月)</t>
+(09年-03月-15日)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -44751,7 +44751,7 @@
           <t>C | 1008呎 (3房)
 $2020万
 $20,038/呎
-(09年-03月)</t>
+(09年-03月-12日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -44759,7 +44759,7 @@
           <t>D | 875呎 (3房)
 $1639万
 $18,729/呎
-(09年-03月)</t>
+(09年-03月-12日)</t>
         </is>
       </c>
     </row>
@@ -44774,7 +44774,7 @@
           <t>A | 1377呎 (4+房)
 $2718万
 $19,738/呎
-(09年-03月)</t>
+(09年-03月-17日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -44782,7 +44782,7 @@
           <t>B | 1281呎 (4+房)
 $2482万
 $19,374/呎
-(09年-03月)</t>
+(09年-03月-18日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -44790,7 +44790,7 @@
           <t>C | 1008呎 (3房)
 $2013万
 $19,969/呎
-(09年-03月)</t>
+(09年-03月-26日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -44798,7 +44798,7 @@
           <t>D | 875呎 (3房)
 $1638万
 $18,715/呎
-(09年-03月)</t>
+(09年-03月-17日)</t>
         </is>
       </c>
     </row>
@@ -44813,7 +44813,7 @@
           <t>A | 1377呎 (4+房)
 $2765万
 $20,077/呎
-(09年-04月)</t>
+(09年-04月-01日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -44821,7 +44821,7 @@
           <t>B | 1281呎 (4+房)
 $2482万
 $19,374/呎
-(09年-03月)</t>
+(09年-03月-17日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -44829,7 +44829,7 @@
           <t>C | 1008呎 (3房)
 $2006万
 $19,901/呎
-(09年-03月)</t>
+(09年-03月-15日)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -44837,7 +44837,7 @@
           <t>D | 875呎 (3房)
 $1636万
 $18,701/呎
-(09年-03月)</t>
+(09年-03月-18日)</t>
         </is>
       </c>
     </row>
@@ -44852,7 +44852,7 @@
           <t>A | 1377呎 (4+房)
 $2699万
 $19,602/呎
-(09年-03月)</t>
+(09年-03月-11日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -44860,7 +44860,7 @@
           <t>B | 1281呎 (4+房)
 $2468万
 $19,266/呎
-(09年-03月)</t>
+(09年-03月-17日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -44868,7 +44868,7 @@
           <t>C | 1031呎 (3房)
 $1999万
 $19,391/呎
-(09年-03月)</t>
+(09年-03月-17日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -44876,7 +44876,7 @@
           <t>D | 875呎 (3房)
 $1635万
 $18,687/呎
-(09年-03月)</t>
+(09年-03月-18日)</t>
         </is>
       </c>
     </row>
@@ -44891,7 +44891,7 @@
           <t>A | 1377呎 (4+房)
 $2681万
 $19,467/呎
-(09年-03月)</t>
+(09年-03月-19日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -44899,7 +44899,7 @@
           <t>B | 1281呎 (4+房)
 $2433万
 $18,991/呎
-(09年-03月)</t>
+(09年-03月-15日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -44907,7 +44907,7 @@
           <t>C | 1008呎 (3房)
 $1992万
 $19,765/呎
-(09年-03月)</t>
+(09年-03月-18日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -44915,7 +44915,7 @@
           <t>D | 875呎 (3房)
 $1635万
 $18,687/呎
-(09年-03月)</t>
+(09年-03月-23日)</t>
         </is>
       </c>
     </row>
@@ -44930,7 +44930,7 @@
           <t>A | 1395呎 (4+房)
 $2744万
 $19,668/呎
-(09年-03月)</t>
+(09年-03月-22日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -44938,7 +44938,7 @@
           <t>B | 1294呎 (4+房)
 $2415万
 $18,663/呎
-(09年-03月)</t>
+(09年-03月-17日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -44946,7 +44946,7 @@
           <t>C | 999呎 (3房)
 $1957万
 $19,587/呎
-(09年-03月)</t>
+(09年-03月-30日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -44954,7 +44954,7 @@
           <t>D | 872呎 (3房)
 $1642万
 $18,833/呎
-(09年-03月)</t>
+(09年-03月-22日)</t>
         </is>
       </c>
     </row>
@@ -44969,7 +44969,7 @@
           <t>A | 1395呎 (4+房)
 $2734万
 $19,600/呎
-(09年-03月)</t>
+(09年-03月-10日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -44977,7 +44977,7 @@
           <t>B | 1265呎 (4+房)
 $2415万
 $19,091/呎
-(09年-03月)</t>
+(09年-03月-15日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -44985,7 +44985,7 @@
           <t>C | 999呎 (3房)
 $1973万
 $19,748/呎
-(09年-03月)</t>
+(09年-03月-09日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -44993,7 +44993,7 @@
           <t>D | 872呎 (3房)
 $1636万
 $18,763/呎
-(09年-03月)</t>
+(09年-03月-15日)</t>
         </is>
       </c>
     </row>
@@ -45008,7 +45008,7 @@
           <t>A | 1394呎 (4+房)
 $2720万
 $19,511/呎
-(09年-03月)</t>
+(09年-03月-22日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -45016,7 +45016,7 @@
           <t>B | 1265呎 (4+房)
 $2415万
 $19,091/呎
-(09年-03月)</t>
+(09年-03月-17日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -45024,7 +45024,7 @@
           <t>C | 999呎 (3房)
 $1973万
 $19,748/呎
-(09年-03月)</t>
+(09年-03月-17日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -45032,7 +45032,7 @@
           <t>D | 916呎 (3房)
 $1624万
 $17,728/呎
-(09年-03月)</t>
+(09年-03月-22日)</t>
         </is>
       </c>
     </row>
@@ -45047,7 +45047,7 @@
           <t>A | 1394呎 (4+房)
 $2720万
 $19,511/呎
-(09年-03月)</t>
+(09年-03月-12日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -45055,7 +45055,7 @@
           <t>B | 1294呎 (4+房)
 $2415万
 $18,663/呎
-(09年-03月)</t>
+(09年-03月-15日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -45063,7 +45063,7 @@
           <t>C | 999呎 (3房)
 $1973万
 $19,748/呎
-(09年-03月)</t>
+(09年-03月-15日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -45071,7 +45071,7 @@
           <t>D | 872呎 (3房)
 $1624万
 $18,623/呎
-(09年-03月)</t>
+(09年-03月-19日)</t>
         </is>
       </c>
     </row>
@@ -45086,7 +45086,7 @@
           <t>A | 1394呎 (4+房)
 $2720万
 $19,511/呎
-(09年-03月)</t>
+(09年-03月-17日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -45094,7 +45094,7 @@
           <t>B | 1265呎 (4+房)
 $2415万
 $19,091/呎
-(09年-03月)</t>
+(09年-03月-12日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -45102,7 +45102,7 @@
           <t>C | 999呎 (3房)
 $2000万
 $20,022/呎
-(09年-03月)</t>
+(09年-03月-17日)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -45110,7 +45110,7 @@
           <t>D | 872呎 (3房)
 $1624万
 $18,623/呎
-(09年-03月)</t>
+(09年-03月-26日)</t>
         </is>
       </c>
     </row>
@@ -45133,7 +45133,7 @@
           <t>B | 1265呎 (4+房)
 $2415万
 $19,091/呎
-(09年-03月)</t>
+(09年-03月-30日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -45141,7 +45141,7 @@
           <t>C | 999呎 (3房)
 $1973万
 $19,748/呎
-(09年-03月)</t>
+(09年-03月-19日)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -45149,7 +45149,7 @@
           <t>D | 872呎 (3房)
 $1618万
 $18,553/呎
-(09年-03月)</t>
+(09年-03月-24日)</t>
         </is>
       </c>
     </row>
@@ -45164,7 +45164,7 @@
           <t>A | 1394呎 (4+房)
 $2720万
 $19,511/呎
-(09年-03月)</t>
+(09年-03月-17日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -45172,7 +45172,7 @@
           <t>B | 1265呎 (4+房)
 $2415万
 $19,091/呎
-(09年-03月)</t>
+(09年-03月-22日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -45180,7 +45180,7 @@
           <t>C | 999呎 (3房)
 $1959万
 $19,611/呎
-(09年-03月)</t>
+(09年-03月-17日)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -45188,7 +45188,7 @@
           <t>D | 872呎 (3房)
 $1618万
 $18,553/呎
-(09年-03月)</t>
+(09年-03月-25日)</t>
         </is>
       </c>
     </row>
@@ -45203,7 +45203,7 @@
           <t>A | 1394呎 (4+房)
 $2720万
 $19,511/呎
-(09年-03月)</t>
+(09年-03月-11日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -45211,7 +45211,7 @@
           <t>B | 1265呎 (4+房)
 $2415万
 $19,091/呎
-(09年-03月)</t>
+(09年-03月-15日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -45219,7 +45219,7 @@
           <t>C | 999呎 (3房)
 $1959万
 $19,611/呎
-(09年-03月)</t>
+(09年-03月-12日)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -45227,7 +45227,7 @@
           <t>D | 872呎 (3房)
 $1618万
 $18,553/呎
-(09年-03月)</t>
+(09年-03月-15日)</t>
         </is>
       </c>
     </row>
@@ -45242,7 +45242,7 @@
           <t>A | 1394呎 (4+房)
 $2701万
 $19,375/呎
-(09年-03月)</t>
+(09年-03月-12日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -45250,7 +45250,7 @@
           <t>B | 1265呎 (4+房)
 $2415万
 $19,091/呎
-(09年-03月)</t>
+(09年-03月-17日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -45258,7 +45258,7 @@
           <t>C | 999呎 (3房)
 $1945万
 $19,473/呎
-(09年-03月)</t>
+(09年-03月-19日)</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -45266,7 +45266,7 @@
           <t>D | 872呎 (3房)
 $1612万
 $18,483/呎
-(09年-04月)</t>
+(09年-04月-01日)</t>
         </is>
       </c>
     </row>
@@ -45281,7 +45281,7 @@
           <t>A | 1391呎 (4+房)
 $2701万
 $19,417/呎
-(09年-03月)</t>
+(09年-03月-18日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -45289,7 +45289,7 @@
           <t>B | 1262呎 (4+房)
 $2425万
 $19,214/呎
-(09年-03月)</t>
+(09年-03月-23日)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -45297,7 +45297,7 @@
           <t>C | 997呎 (3房)
 $1945万
 $19,513/呎
-(09年-03月)</t>
+(09年-03月-17日)</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
@@ -45305,7 +45305,7 @@
           <t>D | 872呎 (3房)
 $1607万
 $18,427/呎
-(09年-03月)</t>
+(09年-03月-12日)</t>
         </is>
       </c>
     </row>
@@ -45320,7 +45320,7 @@
           <t>A | 1391呎 (4+房)
 $2682万
 $19,280/呎
-(09年-03月)</t>
+(09年-03月-17日)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -45328,7 +45328,7 @@
           <t>B | 1262呎 (4+房)
 $2407万
 $19,073/呎
-(09年-03月)</t>
+(09年-03月-22日)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -45336,7 +45336,7 @@
           <t>C | 997呎 (3房)
 $1945万
 $19,513/呎
-(09年-03月)</t>
+(09年-03月-17日)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -45344,7 +45344,7 @@
           <t>D | 872呎 (3房)
 $1159万
 $13,290/呎
-(09年-03月)</t>
+(09年-03月-15日)</t>
         </is>
       </c>
     </row>
@@ -45359,7 +45359,7 @@
           <t>A | 1391呎 (4+房)
 $2682万
 $19,280/呎
-(09年-03月)</t>
+(09年-03月-16日)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -45367,7 +45367,7 @@
           <t>B | 1262呎 (4+房)
 $2390万
 $18,939/呎
-(09年-03月)</t>
+(09年-03月-17日)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -45375,7 +45375,7 @@
           <t>C | 997呎 (3房)
 $1945万
 $19,513/呎
-(09年-03月)</t>
+(09年-03月-16日)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -45383,7 +45383,7 @@
           <t>D | 872呎 (3房)
 $1606万
 $18,413/呎
-(09年-03月)</t>
+(09年-03月-15日)</t>
         </is>
       </c>
     </row>
@@ -45398,7 +45398,7 @@
           <t>A | 1391呎 (4+房)
 $2682万
 $19,280/呎
-(09年-03月)</t>
+(09年-03月-22日)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -45406,7 +45406,7 @@
           <t>B | 1262呎 (4+房)
 $2390万
 $18,939/呎
-(09年-03月)</t>
+(09年-03月-17日)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -45414,7 +45414,7 @@
           <t>C | 997呎 (3房)
 $1945万
 $19,513/呎
-(09年-03月)</t>
+(09年-03月-17日)</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
@@ -45422,7 +45422,7 @@
           <t>D | 872呎 (3房)
 $1587万
 $18,203/呎
-(09年-04月)</t>
+(09年-04月-01日)</t>
         </is>
       </c>
     </row>
@@ -45437,7 +45437,7 @@
           <t>A | 1391呎 (4+房)
 $2672万
 $19,211/呎
-(09年-03月)</t>
+(09年-03月-11日)</t>
         </is>
       </c>
       <c r="C29" s="22" t="inlineStr">
@@ -45445,7 +45445,7 @@
           <t>B | 1262呎 (4+房)
 $2382万
 $18,871/呎
-(09年-03月)</t>
+(09年-03月-15日)</t>
         </is>
       </c>
       <c r="D29" s="22" t="inlineStr">
@@ -45453,7 +45453,7 @@
           <t>C | 997呎 (3房)
 $1945万
 $19,513/呎
-(09年-03月)</t>
+(09年-03月-17日)</t>
         </is>
       </c>
       <c r="E29" s="22" t="inlineStr">
@@ -45461,7 +45461,7 @@
           <t>D | 872呎 (3房)
 $1587万
 $18,203/呎
-(09年-03月)</t>
+(09年-03月-22日)</t>
         </is>
       </c>
     </row>
@@ -45476,7 +45476,7 @@
           <t>A | 1391呎 (4+房)
 $2663万
 $19,143/呎
-(09年-03月)</t>
+(09年-03月-30日)</t>
         </is>
       </c>
       <c r="C30" s="22" t="inlineStr">
@@ -45484,7 +45484,7 @@
           <t>B | 1262呎 (4+房)
 $2373万
 $18,802/呎
-(09年-03月)</t>
+(09年-03月-22日)</t>
         </is>
       </c>
       <c r="D30" s="22" t="inlineStr">
@@ -45492,7 +45492,7 @@
           <t>C | 997呎 (3房)
 $1932万
 $19,375/呎
-(09年-03月)</t>
+(09年-03月-17日)</t>
         </is>
       </c>
       <c r="E30" s="22" t="inlineStr">
@@ -45500,7 +45500,7 @@
           <t>D | 872呎 (3房)
 $1581万
 $18,133/呎
-(09年-03月)</t>
+(09年-03月-29日)</t>
         </is>
       </c>
     </row>
@@ -45515,7 +45515,7 @@
           <t>A | 1391呎 (4+房)
 $2644万
 $19,006/呎
-(09年-03月)</t>
+(09年-03月-12日)</t>
         </is>
       </c>
       <c r="C31" s="22" t="inlineStr">
@@ -45523,7 +45523,7 @@
           <t>B | 1262呎 (4+房)
 $2338万
 $18,528/呎
-(09年-03月)</t>
+(09年-03月-18日)</t>
         </is>
       </c>
       <c r="D31" s="22" t="inlineStr">
@@ -45531,7 +45531,7 @@
           <t>C | 997呎 (3房)
 $1925万
 $19,306/呎
-(09年-03月)</t>
+(09年-03月-15日)</t>
         </is>
       </c>
       <c r="E31" s="22" t="inlineStr">
@@ -45539,7 +45539,7 @@
           <t>D | 872呎 (3房)
 $1575万
 $18,063/呎
-(09年-03月)</t>
+(09年-03月-22日)</t>
         </is>
       </c>
     </row>
@@ -45554,7 +45554,7 @@
           <t>A | 1391呎 (4+房)
 $2643万
 $19,001/呎
-(09年-03月)</t>
+(09年-03月-25日)</t>
         </is>
       </c>
       <c r="C32" s="22" t="inlineStr">
@@ -45562,7 +45562,7 @@
           <t>B | 1262呎 (4+房)
 $2338万
 $18,528/呎
-(09年-03月)</t>
+(09年-03月-17日)</t>
         </is>
       </c>
       <c r="D32" s="22" t="inlineStr">
@@ -45570,7 +45570,7 @@
           <t>C | 997呎 (3房)
 $1918万
 $19,238/呎
-(09年-03月)</t>
+(09年-03月-29日)</t>
         </is>
       </c>
       <c r="E32" s="22" t="inlineStr">
@@ -45578,7 +45578,7 @@
           <t>D | 872呎 (3房)
 $1575万
 $18,063/呎
-(09年-03月)</t>
+(09年-03月-25日)</t>
         </is>
       </c>
     </row>
@@ -45593,7 +45593,7 @@
           <t>A | 1391呎 (4+房)
 $2634万
 $18,938/呎
-(09年-03月)</t>
+(09年-03月-17日)</t>
         </is>
       </c>
       <c r="C33" s="22" t="inlineStr">
@@ -45601,7 +45601,7 @@
           <t>B | 1262呎 (4+房)
 $2330万
 $18,463/呎
-(09年-03月)</t>
+(09年-03月-18日)</t>
         </is>
       </c>
       <c r="D33" s="22" t="inlineStr">
@@ -45609,7 +45609,7 @@
           <t>C | 997呎 (3房)
 $1911万
 $19,169/呎
-(09年-03月)</t>
+(09年-03月-19日)</t>
         </is>
       </c>
       <c r="E33" s="22" t="inlineStr">
@@ -45617,7 +45617,7 @@
           <t>D | 916呎 (3房)
 $1563万
 $17,062/呎
-(09年-03月)</t>
+(09年-03月-18日)</t>
         </is>
       </c>
     </row>
@@ -45632,7 +45632,7 @@
           <t>A | 1391呎 (4+房)
 $2634万
 $18,936/呎
-(09年-03月)</t>
+(09年-03月-17日)</t>
         </is>
       </c>
       <c r="C34" s="22" t="inlineStr">
@@ -45640,7 +45640,7 @@
           <t>B | 1262呎 (4+房)
 $2330万
 $18,459/呎
-(09年-03月)</t>
+(09年-03月-22日)</t>
         </is>
       </c>
       <c r="D34" s="22" t="inlineStr">
@@ -45648,7 +45648,7 @@
           <t>C | 997呎 (3房)
 $1908万
 $19,142/呎
-(09年-03月)</t>
+(09年-03月-24日)</t>
         </is>
       </c>
       <c r="E34" s="22" t="inlineStr">
@@ -45656,7 +45656,7 @@
           <t>D | 872呎 (3房)
 $1563万
 $17,923/呎
-(09年-03月)</t>
+(09年-03月-17日)</t>
         </is>
       </c>
     </row>
@@ -45671,7 +45671,7 @@
           <t>A | 1391呎 (4+房)
 $2625万
 $18,870/呎
-(09年-03月)</t>
+(09年-03月-11日)</t>
         </is>
       </c>
       <c r="C35" s="22" t="inlineStr">
@@ -45679,7 +45679,7 @@
           <t>B | 1262呎 (4+房)
 $2321万
 $18,390/呎
-(09年-03月)</t>
+(09年-03月-24日)</t>
         </is>
       </c>
       <c r="D35" s="22" t="inlineStr">
@@ -45687,7 +45687,7 @@
           <t>C | 1028呎 (3房)
 $1904万
 $18,524/呎
-(09年-03月)</t>
+(09年-03月-19日)</t>
         </is>
       </c>
       <c r="E35" s="22" t="inlineStr">
@@ -45695,7 +45695,7 @@
           <t>D | 872呎 (3房)
 $1551万
 $17,783/呎
-(09年-03月)</t>
+(09年-03月-12日)</t>
         </is>
       </c>
     </row>
@@ -45710,7 +45710,7 @@
           <t>A | 1391呎 (4+房)
 $2615万
 $18,801/呎
-(09年-03月)</t>
+(09年-03月-17日)</t>
         </is>
       </c>
       <c r="C36" s="22" t="inlineStr">
@@ -45718,7 +45718,7 @@
           <t>B | 1262呎 (4+房)
 $2321万
 $18,390/呎
-(09年-03月)</t>
+(09年-03月-17日)</t>
         </is>
       </c>
       <c r="D36" s="22" t="inlineStr">
@@ -45726,7 +45726,7 @@
           <t>C | 997呎 (3房)
 $1891万
 $18,963/呎
-(09年-03月)</t>
+(09年-03月-26日)</t>
         </is>
       </c>
       <c r="E36" s="22" t="inlineStr">
@@ -45734,7 +45734,7 @@
           <t>D | 872呎 (3房)
 $1532万
 $17,573/呎
-(09年-03月)</t>
+(09年-03月-18日)</t>
         </is>
       </c>
     </row>
@@ -45749,7 +45749,7 @@
           <t>A | 1391呎 (4+房)
 $2602万
 $18,706/呎
-(09年-03月)</t>
+(09年-03月-18日)</t>
         </is>
       </c>
       <c r="C37" s="22" t="inlineStr">
@@ -45757,7 +45757,7 @@
           <t>B | 1262呎 (4+房)
 $2317万
 $18,363/呎
-(09年-03月)</t>
+(09年-03月-22日)</t>
         </is>
       </c>
       <c r="D37" s="22" t="inlineStr">
@@ -45765,7 +45765,7 @@
           <t>C | 997呎 (3房)
 $1888万
 $18,935/呎
-(09年-03月)</t>
+(09年-03月-10日)</t>
         </is>
       </c>
       <c r="E37" s="22" t="inlineStr">
@@ -45773,7 +45773,7 @@
           <t>D | 872呎 (3房)
 $1526万
 $17,503/呎
-(09年-03月)</t>
+(09年-03月-26日)</t>
         </is>
       </c>
     </row>
@@ -45918,7 +45918,7 @@
           <t>B | 1419呎 (4+房)
 $5497万
 $38,738/呎
-(13年-11月)</t>
+(13年-11月-24日)</t>
         </is>
       </c>
       <c r="D5" s="22" t="inlineStr">
@@ -45926,7 +45926,7 @@
           <t>C | 1175呎 (3房)
 $6857万
 $58,357/呎
-(13年-12月)</t>
+(13年-12月-19日)</t>
         </is>
       </c>
       <c r="E5" s="21" t="inlineStr"/>
@@ -45935,7 +45935,7 @@
           <t>E | 684呎 (2房)
 $2285万
 $33,408/呎
-(13年-11月)</t>
+(13年-11月-21日)</t>
         </is>
       </c>
     </row>
@@ -45951,7 +45951,7 @@
           <t>B | 1404呎 (4+房)
 $8393万
 $59,777/呎
-(13年-11月)</t>
+(13年-11月-26日)</t>
         </is>
       </c>
       <c r="D6" s="22" t="inlineStr">
@@ -45959,7 +45959,7 @@
           <t>C | 658呎 (2房)
 $2188万
 $33,256/呎
-(13年-11月)</t>
+(13年-11月-24日)</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
@@ -45967,7 +45967,7 @@
           <t>D | 672呎 (2房)
 $2192万
 $32,621/呎
-(13年-11月)</t>
+(13年-11月-21日)</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
@@ -45975,7 +45975,7 @@
           <t>E | 684呎 (2房)
 $3729万
 $54,521/呎
-(13年-10月)</t>
+(13年-10月-24日)</t>
         </is>
       </c>
     </row>
@@ -45990,7 +45990,7 @@
           <t>A | 935呎 (3房)
 $3111万
 $33,270/呎
-(13年-11月)</t>
+(13年-11月-13日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -45998,7 +45998,7 @@
           <t>B | 1075呎 (4+房)
 $3730万
 $34,700/呎
-(13年-11月)</t>
+(13年-11月-11日)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -46006,7 +46006,7 @@
           <t>C | 658呎 (2房)
 $2098万
 $31,885/呎
-(13年-11月)</t>
+(13年-11月-11日)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -46014,7 +46014,7 @@
           <t>D | 672呎 (2房)
 $2059万
 $30,633/呎
-(13年-11月)</t>
+(13年-11月-11日)</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr">
@@ -46022,7 +46022,7 @@
           <t>E | 674呎 (2房)
 $2061万
 $30,580/呎
-(13年-11月)</t>
+(13年-11月-14日)</t>
         </is>
       </c>
     </row>
@@ -46037,7 +46037,7 @@
           <t>A | 900呎 (3房)
 $2846万
 $31,617/呎
-(13年-11月)</t>
+(13年-11月-12日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -46045,7 +46045,7 @@
           <t>B | 1128呎 (4+房)
 $3636万
 $32,233/呎
-(13年-11月)</t>
+(13年-11月-10日)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -46053,7 +46053,7 @@
           <t>C | 658呎 (2房)
 $1977万
 $30,051/呎
-(13年-11月)</t>
+(13年-11月-12日)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -46061,7 +46061,7 @@
           <t>D | 672呎 (2房)
 $1981万
 $29,478/呎
-(13年-11月)</t>
+(13年-11月-07日)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
@@ -46069,7 +46069,7 @@
           <t>E | 674呎 (2房)
 $1983万
 $29,423/呎
-(13年-11月)</t>
+(13年-11月-07日)</t>
         </is>
       </c>
     </row>
@@ -46084,7 +46084,7 @@
           <t>A | 900呎 (3房)
 $2826万
 $31,398/呎
-(13年-11月)</t>
+(13年-11月-12日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -46092,7 +46092,7 @@
           <t>B | 1161呎 (4+房)
 $3611万
 $31,099/呎
-(13年-11月)</t>
+(13年-11月-07日)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -46100,7 +46100,7 @@
           <t>C | 658呎 (2房)
 $1964万
 $29,841/呎
-(13年-11月)</t>
+(13年-11月-07日)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -46108,7 +46108,7 @@
           <t>D | 672呎 (2房)
 $1967万
 $29,272/呎
-(13年-11月)</t>
+(13年-11月-12日)</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
@@ -46116,7 +46116,7 @@
           <t>E | 674呎 (2房)
 $1969万
 $29,219/呎
-(13年-11月)</t>
+(13年-11月-06日)</t>
         </is>
       </c>
     </row>
@@ -46131,7 +46131,7 @@
           <t>A | 900呎 (3房)
 $2629万
 $29,208/呎
-(13年-10月)</t>
+(13年-10月-31日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -46139,7 +46139,7 @@
           <t>B | 1161呎 (4+房)
 $3289万
 $28,332/呎
-(13年-10月)</t>
+(13年-10月-31日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -46147,7 +46147,7 @@
           <t>C | 658呎 (2房)
 $1781万
 $27,063/呎
-(13年-11月)</t>
+(13年-11月-10日)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -46155,7 +46155,7 @@
           <t>D | 672呎 (2房)
 $1784万
 $26,548/呎
-(13年-11月)</t>
+(13年-11月-06日)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -46163,7 +46163,7 @@
           <t>E | 674呎 (2房)
 $1794万
 $26,620/呎
-(13年-10月)</t>
+(13年-10月-31日)</t>
         </is>
       </c>
     </row>
@@ -46178,7 +46178,7 @@
           <t>A | 900呎 (3房)
 $2557万
 $28,406/呎
-(13年-11月)</t>
+(13年-11月-05日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -46186,7 +46186,7 @@
           <t>B | 1128呎 (4+房)
 $3267万
 $28,959/呎
-(13年-10月)</t>
+(13年-10月-31日)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -46194,7 +46194,7 @@
           <t>C | 658呎 (2房)
 $1768万
 $26,876/呎
-(13年-10月)</t>
+(13年-10月-31日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -46202,7 +46202,7 @@
           <t>D | 672呎 (2房)
 $1772万
 $26,362/呎
-(13年-10月)</t>
+(13年-10月-31日)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -46210,7 +46210,7 @@
           <t>E | 674呎 (2房)
 $1782万
 $26,435/呎
-(13年-10月)</t>
+(13年-10月-31日)</t>
         </is>
       </c>
     </row>
@@ -46225,7 +46225,7 @@
           <t>A | 900呎 (3房)
 $2539万
 $28,209/呎
-(13年-11月)</t>
+(13年-11月-03日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -46233,7 +46233,7 @@
           <t>B | 1128呎 (4+房)
 $3244万
 $28,758/呎
-(13年-11月)</t>
+(13年-11月-11日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -46241,7 +46241,7 @@
           <t>C | 658呎 (2房)
 $1756万
 $26,688/呎
-(13年-10月)</t>
+(13年-10月-31日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -46249,7 +46249,7 @@
           <t>D | 672呎 (2房)
 $1759万
 $26,180/呎
-(13年-11月)</t>
+(13年-11月-07日)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -46257,7 +46257,7 @@
           <t>E | 674呎 (2房)
 $1769万
 $26,250/呎
-(13年-10月)</t>
+(13年-10月-31日)</t>
         </is>
       </c>
     </row>
@@ -46272,7 +46272,7 @@
           <t>A | 900呎 (3房)
 $4241万
 $47,122/呎
-(13年-10月)</t>
+(13年-10月-11日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -46280,7 +46280,7 @@
           <t>B | 1128呎 (4+房)
 $3221万
 $28,557/呎
-(13年-10月)</t>
+(13年-10月-31日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -46288,7 +46288,7 @@
           <t>C | 658呎 (2房)
 $1744万
 $26,503/呎
-(13年-10月)</t>
+(13年-10月-31日)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -46296,7 +46296,7 @@
           <t>D | 672呎 (2房)
 $1747万
 $25,998/呎
-(13年-10月)</t>
+(13年-10月-31日)</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -46304,7 +46304,7 @@
           <t>E | 684呎 (2房)
 $3418万
 $49,976/呎
-(13年-10月)</t>
+(13年-10月-11日)</t>
         </is>
       </c>
     </row>
@@ -46319,7 +46319,7 @@
           <t>A | 900呎 (3房)
 $2736万
 $30,395/呎
-(13年-11月)</t>
+(13年-11月-11日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -46327,7 +46327,7 @@
           <t>B | 1128呎 (4+房)
 $3495万
 $30,984/呎
-(13年-11月)</t>
+(13年-11月-18日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -46335,7 +46335,7 @@
           <t>C | 658呎 (2房)
 $1901万
 $28,888/呎
-(13年-11月)</t>
+(13年-11月-12日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -46343,7 +46343,7 @@
           <t>D | 672呎 (2房)
 $1904万
 $28,337/呎
-(13年-11月)</t>
+(13年-11月-07日)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -46351,7 +46351,7 @@
           <t>E | 674呎 (2房)
 $1906万
 $28,284/呎
-(13年-11月)</t>
+(13年-11月-06日)</t>
         </is>
       </c>
     </row>
@@ -46366,7 +46366,7 @@
           <t>A | 900呎 (3房)
 $2486万
 $27,626/呎
-(13年-11月)</t>
+(13年-11月-07日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -46374,7 +46374,7 @@
           <t>B | 1128呎 (4+房)
 $11993万
 $106,317/呎
-(13年-10月)</t>
+(13年-10月-11日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -46382,7 +46382,7 @@
           <t>C | 658呎 (2房)
 $4241万
 $64,453/呎
-(13年-10月)</t>
+(13年-10月-11日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -46390,7 +46390,7 @@
           <t>D | 679呎 (2房)
 $1723万
 $25,374/呎
-(13年-11月)</t>
+(13年-11月-06日)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -46398,7 +46398,7 @@
           <t>E | 674呎 (2房)
 $1769万
 $26,249/呎
-(13年-11月)</t>
+(13年-11月-05日)</t>
         </is>
       </c>
     </row>
@@ -46413,7 +46413,7 @@
           <t>A | 900呎 (3房)
 $11993万
 $133,250/呎
-(13年-10月)</t>
+(13年-10月-11日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -46421,7 +46421,7 @@
           <t>B | 1128呎 (4+房)
 $4863万
 $43,109/呎
-(13年-10月)</t>
+(13年-10月-11日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -46429,7 +46429,7 @@
           <t>C | 658呎 (2房)
 $4863万
 $73,901/呎
-(13年-10月)</t>
+(13年-10月-11日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -46437,7 +46437,7 @@
           <t>D | 672呎 (2房)
 $1711万
 $25,461/呎
-(13年-11月)</t>
+(13年-11月-03日)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -46445,7 +46445,7 @@
           <t>E | 674呎 (2房)
 $1721万
 $25,530/呎
-(13年-11月)</t>
+(13年-11月-04日)</t>
         </is>
       </c>
     </row>
@@ -46460,7 +46460,7 @@
           <t>A | 900呎 (3房)
 $2452万
 $27,242/呎
-(13年-11月)</t>
+(13年-11月-03日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -46468,7 +46468,7 @@
           <t>B | 1128呎 (4+房)
 $3133万
 $27,771/呎
-(13年-11月)</t>
+(13年-11月-04日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -46476,7 +46476,7 @@
           <t>C | 658呎 (2房)
 $1696万
 $25,774/呎
-(13年-11月)</t>
+(13年-11月-06日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -46484,7 +46484,7 @@
           <t>D | 672呎 (2房)
 $1699万
 $25,282/呎
-(13年-11月)</t>
+(13年-11月-06日)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -46492,7 +46492,7 @@
           <t>E | 674呎 (2房)
 $1709万
 $25,351/呎
-(13年-11月)</t>
+(13年-11月-03日)</t>
         </is>
       </c>
     </row>
@@ -46507,7 +46507,7 @@
           <t>A | 900呎 (3房)
 $2751万
 $30,569/呎
-(13年-11月)</t>
+(13年-11月-11日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -46515,7 +46515,7 @@
           <t>B | 1128呎 (4+房)
 $3577万
 $31,714/呎
-(13年-11月)</t>
+(13年-11月-11日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -46523,7 +46523,7 @@
           <t>C | 658呎 (2房)
 $1886万
 $28,665/呎
-(13年-11月)</t>
+(13年-11月-24日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -46531,7 +46531,7 @@
           <t>D | 679呎 (2房)
 $3749万
 $55,218/呎
-(13年-10月)</t>
+(13年-10月-19日)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -46539,7 +46539,7 @@
           <t>E | 674呎 (2房)
 $1892万
 $28,069/呎
-(13年-11月)</t>
+(13年-11月-11日)</t>
         </is>
       </c>
     </row>
@@ -46554,7 +46554,7 @@
           <t>A | 900呎 (3房)
 $2732万
 $30,354/呎
-(13年-11月)</t>
+(13年-11月-07日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -46562,7 +46562,7 @@
           <t>B | 1128呎 (4+房)
 $3552万
 $31,491/呎
-(13年-11月)</t>
+(13年-11月-12日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -46570,7 +46570,7 @@
           <t>C | 658呎 (2房)
 $1873万
 $28,464/呎
-(13年-11月)</t>
+(13年-11月-07日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -46578,7 +46578,7 @@
           <t>D | 672呎 (2房)
 $1876万
 $27,920/呎
-(13年-11月)</t>
+(13年-11月-11日)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -46586,7 +46586,7 @@
           <t>E | 674呎 (2房)
 $1879万
 $27,873/呎
-(13年-11月)</t>
+(13年-11月-14日)</t>
         </is>
       </c>
     </row>
@@ -46601,7 +46601,7 @@
           <t>A | 928呎 (3房)
 $2713万
 $29,232/呎
-(13年-11月)</t>
+(13年-11月-11日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -46609,7 +46609,7 @@
           <t>B | 1161呎 (4+房)
 $3527万
 $30,383/呎
-(13年-11月)</t>
+(13年-11月-11日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -46617,7 +46617,7 @@
           <t>C | 669呎 (2房)
 $3749万
 $56,043/呎
-(13年-10月)</t>
+(13年-10月-19日)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -46625,7 +46625,7 @@
           <t>D | 672呎 (2房)
 $1863万
 $27,725/呎
-(13年-11月)</t>
+(13年-11月-17日)</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -46633,7 +46633,7 @@
           <t>E | 674呎 (2房)
 $1865万
 $27,677/呎
-(13年-11月)</t>
+(13年-11月-11日)</t>
         </is>
       </c>
     </row>
@@ -46648,7 +46648,7 @@
           <t>A | 900呎 (3房)
 $2384万
 $26,487/呎
-(13年-11月)</t>
+(13年-11月-04日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -46656,7 +46656,7 @@
           <t>B | 1128呎 (4+房)
 $11993万
 $106,317/呎
-(13年-10月)</t>
+(13年-10月-11日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -46664,7 +46664,7 @@
           <t>C | 658呎 (2房)
 $11993万
 $182,257/呎
-(13年-10月)</t>
+(13年-10月-11日)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -46672,7 +46672,7 @@
           <t>D | 672呎 (2房)
 $11993万
 $178,460/呎
-(13年-10月)</t>
+(13年-10月-11日)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -46680,7 +46680,7 @@
           <t>E | 684呎 (2房)
 $3418万
 $49,976/呎
-(13年-10月)</t>
+(13年-10月-11日)</t>
         </is>
       </c>
     </row>
@@ -46695,7 +46695,7 @@
           <t>A | 928呎 (3房)
 $2675万
 $28,825/呎
-(13年-11月)</t>
+(13年-11月-11日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -46703,7 +46703,7 @@
           <t>B | 1128呎 (4+房)
 $3478万
 $30,835/呎
-(13年-11月)</t>
+(13年-11月-17日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -46711,7 +46711,7 @@
           <t>C | 658呎 (2房)
 $1834万
 $27,871/呎
-(13年-11月)</t>
+(13年-11月-12日)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -46719,7 +46719,7 @@
           <t>D | 672呎 (2房)
 $1837万
 $27,339/呎
-(13年-11月)</t>
+(13年-11月-11日)</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -46727,7 +46727,7 @@
           <t>E | 674呎 (2房)
 $1839万
 $27,291/呎
-(13年-11月)</t>
+(13年-11月-11日)</t>
         </is>
       </c>
     </row>
@@ -46742,7 +46742,7 @@
           <t>A | 900呎 (3房)
 $2805万
 $31,168/呎
-(13年-11月)</t>
+(13年-11月-18日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -46750,7 +46750,7 @@
           <t>B | 1128呎 (4+房)
 $3737万
 $33,127/呎
-(13年-11月)</t>
+(13年-11月-18日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -46758,7 +46758,7 @@
           <t>C | 658呎 (2房)
 $1929万
 $29,314/呎
-(13年-11月)</t>
+(13年-11月-18日)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -46766,7 +46766,7 @@
           <t>D | 672呎 (2房)
 $1927万
 $28,682/呎
-(13年-11月)</t>
+(13年-11月-18日)</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -46774,7 +46774,7 @@
           <t>E | 674呎 (2房)
 $1930万
 $28,637/呎
-(13年-11月)</t>
+(13年-11月-21日)</t>
         </is>
       </c>
     </row>
@@ -46789,7 +46789,7 @@
           <t>A | 900呎 (3房)
 $2580万
 $28,668/呎
-(13年-11月)</t>
+(13年-11月-21日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -46797,7 +46797,7 @@
           <t>B | 1161呎 (4+房)
 $3634万
 $31,301/呎
-(13年-11月)</t>
+(13年-11月-25日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -46805,7 +46805,7 @@
           <t>C | 658呎 (2房)
 $1915万
 $29,108/呎
-(13年-11月)</t>
+(13年-11月-21日)</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -46813,7 +46813,7 @@
           <t>D | 679呎 (2房)
 $1914万
 $28,188/呎
-(13年-11月)</t>
+(13年-11月-24日)</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -46821,7 +46821,7 @@
           <t>E | 674呎 (2房)
 $1917万
 $28,437/呎
-(13年-11月)</t>
+(13年-11月-26日)</t>
         </is>
       </c>
     </row>
@@ -46836,7 +46836,7 @@
           <t>A | 900呎 (3房)
 $2764万
 $30,708/呎
-(13年-11月)</t>
+(13年-11月-20日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -46844,7 +46844,7 @@
           <t>B | 1128呎 (4+房)
 $7317万
 $64,868/呎
-(13年-10月)</t>
+(13年-10月-24日)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -46852,7 +46852,7 @@
           <t>C | 669呎 (2房)
 $1902万
 $28,429/呎
-(13年-11月)</t>
+(13年-11月-27日)</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
@@ -46860,7 +46860,7 @@
           <t>D | 672呎 (2房)
 $1901万
 $28,282/呎
-(13年-11月)</t>
+(13年-11月-24日)</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -46868,7 +46868,7 @@
           <t>E | 674呎 (2房)
 $1903万
 $28,238/呎
-(13年-11月)</t>
+(13年-11月-14日)</t>
         </is>
       </c>
     </row>
@@ -46884,7 +46884,7 @@
           <t>B | 1165呎 (4+房)
 $7317万
 $62,808/呎
-(13年-10月)</t>
+(13年-10月-24日)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -46892,7 +46892,7 @@
           <t>C | 658呎 (2房)
 $1900万
 $28,872/呎
-(13年-11月)</t>
+(13年-11月-21日)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -46900,7 +46900,7 @@
           <t>D | 683呎 (2房)
 $1909万
 $27,952/呎
-(13年-11月)</t>
+(13年-11月-21日)</t>
         </is>
       </c>
       <c r="F26" s="21" t="inlineStr"/>
@@ -46916,7 +46916,7 @@
           <t>A | 2514呎 (4+房)
 $20100万
 $79,952/呎
-(21年-07月)</t>
+(21年-07月-08日)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -46924,7 +46924,7 @@
           <t>B | 1157呎 (4+房)
 $7520万
 $65,000/呎
-(23年-03月)</t>
+(23年-03月-28日)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -46932,7 +46932,7 @@
           <t>C | 658呎 (2房)
 $1896万
 $28,816/呎
-(13年-11月)</t>
+(13年-11月-14日)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -46940,7 +46940,7 @@
           <t>D | 676呎 (2房)
 $1896万
 $28,045/呎
-(13年-11月)</t>
+(13年-11月-18日)</t>
         </is>
       </c>
       <c r="F27" s="21" t="inlineStr"/>
@@ -47093,7 +47093,7 @@
           <t>B | 1493呎 (4+房)
 $15689万
 $105,082/呎
-(23年-12月)</t>
+(23年-12月-07日)</t>
         </is>
       </c>
       <c r="D5" s="21" t="inlineStr"/>
@@ -47118,7 +47118,7 @@
           <t>A | 949呎 (3房)
 $3494万
 $36,816/呎
-(13年-11月)</t>
+(13年-11月-19日)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -47126,7 +47126,7 @@
           <t>B | 1040呎 (4+房)
 $6412万
 $61,653/呎
-(24年-03月)</t>
+(24年-03月-25日)</t>
         </is>
       </c>
       <c r="D6" s="23" t="inlineStr">
@@ -47142,7 +47142,7 @@
           <t>D | 1020呎 (4+房)
 $5880万
 $57,647/呎
-(23年-06月)</t>
+(23年-06月-04日)</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
@@ -47150,7 +47150,7 @@
           <t>E | 910呎 (3房)
 $3950万
 $43,408/呎
-(13年-12月)</t>
+(13年-12月-23日)</t>
         </is>
       </c>
     </row>
@@ -47165,7 +47165,7 @@
           <t>A | 949呎 (3房)
 $3449万
 $36,344/呎
-(13年-11月)</t>
+(13年-11月-11日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -47173,7 +47173,7 @@
           <t>B | 1040呎 (4+房)
 $6294万
 $60,522/呎
-(24年-03月)</t>
+(24年-03月-25日)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -47181,7 +47181,7 @@
           <t>C | 1608呎 (3房)
 $13073万
 $81,300/呎
-(21年-10月)</t>
+(21年-10月-03日)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -47189,7 +47189,7 @@
           <t>D | 1070呎 (4+房)
 $5500万
 $51,402/呎
-(23年-01月)</t>
+(23年-01月-19日)</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr">
@@ -47197,7 +47197,7 @@
           <t>E | 910呎 (3房)
 $3899万
 $42,851/呎
-(13年-12月)</t>
+(13年-12月-22日)</t>
         </is>
       </c>
     </row>
@@ -47212,7 +47212,7 @@
           <t>A | 949呎 (3房)
 $6411万
 $67,559/呎
-(13年-10月)</t>
+(13年-10月-15日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -47220,7 +47220,7 @@
           <t>B | 1093呎 (4+房)
 $6028万
 $55,151/呎
-(23年-09月)</t>
+(23年-09月-20日)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -47228,7 +47228,7 @@
           <t>C | 1580呎 (4+房)
 $12334万
 $78,063/呎
-(18年-10月)</t>
+(18年-10月-03日)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -47236,7 +47236,7 @@
           <t>D | 1070呎 (4+房)
 $4355万
 $40,698/呎
-(10年-11月)</t>
+(10年-11月-30日)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
@@ -47244,7 +47244,7 @@
           <t>E | 910呎 (3房)
 $3754万
 $41,252/呎
-(13年-11月)</t>
+(13年-11月-26日)</t>
         </is>
       </c>
     </row>
@@ -47259,7 +47259,7 @@
           <t>A | 949呎 (3房)
 $2961万
 $31,198/呎
-(13年-10月)</t>
+(13年-10月-31日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -47267,7 +47267,7 @@
           <t>B | 1093呎 (4+房)
 $5341万
 $48,863/呎
-(17年-04月)</t>
+(17年-04月-10日)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -47275,7 +47275,7 @@
           <t>C | 1580呎 (4+房)
 $8173万
 $51,727/呎
-(16年-11月)</t>
+(16年-11月-03日)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -47283,7 +47283,7 @@
           <t>D | 1091呎 (4+房)
 $4115万
 $37,716/呎
-(10年-10月)</t>
+(10年-10月-25日)</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
@@ -47291,7 +47291,7 @@
           <t>E | 933呎 (3房)
 $3706万
 $39,719/呎
-(13年-11月)</t>
+(13年-11月-26日)</t>
         </is>
       </c>
     </row>
@@ -47306,7 +47306,7 @@
           <t>A | 949呎 (3房)
 $2942万
 $30,997/呎
-(13年-11月)</t>
+(13年-11月-04日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -47314,7 +47314,7 @@
           <t>B | 1093呎 (4+房)
 $5325万
 $48,715/呎
-(16年-09月)</t>
+(16年-09月-19日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -47322,7 +47322,7 @@
           <t>C | 1580呎 (4+房)
 $8313万
 $52,611/呎
-(16年-09月)</t>
+(16年-09月-27日)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -47330,7 +47330,7 @@
           <t>D | 1070呎 (4+房)
 $3926万
 $36,690/呎
-(10年-10月)</t>
+(10年-10月-20日)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -47338,7 +47338,7 @@
           <t>E | 910呎 (3房)
 $3596万
 $39,519/呎
-(13年-11月)</t>
+(13年-11月-19日)</t>
         </is>
       </c>
     </row>
@@ -47353,7 +47353,7 @@
           <t>A | 963呎 (3房)
 $5826万
 $60,501/呎
-(13年-10月)</t>
+(13年-10月-11日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -47361,7 +47361,7 @@
           <t>B | 1093呎 (4+房)
 $5113万
 $46,782/呎
-(15年-12月)</t>
+(15年-12月-20日)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -47369,7 +47369,7 @@
           <t>C | 1521呎 (4+房)
 $7825万
 $51,445/呎
-(16年-09月)</t>
+(16年-09月-14日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -47377,7 +47377,7 @@
           <t>D | 1070呎 (4+房)
 $3809万
 $35,603/呎
-(10年-07月)</t>
+(10年-07月-13日)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -47385,7 +47385,7 @@
           <t>E | 910呎 (3房)
 $3346万
 $36,771/呎
-(13年-11月)</t>
+(13年-11月-11日)</t>
         </is>
       </c>
     </row>
@@ -47400,7 +47400,7 @@
           <t>A | 963呎 (3房)
 $5826万
 $60,501/呎
-(13年-10月)</t>
+(13年-10月-11日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -47408,7 +47408,7 @@
           <t>B | 1093呎 (4+房)
 $5251万
 $48,040/呎
-(16年-08月)</t>
+(16年-08月-10日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -47416,7 +47416,7 @@
           <t>C | 1580呎 (4+房)
 $6325万
 $40,030/呎
-(10年-04月)</t>
+(10年-04月-21日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -47424,7 +47424,7 @@
           <t>D | 1070呎 (4+房)
 $3809万
 $35,603/呎
-(10年-11月)</t>
+(10年-11月-11日)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -47432,7 +47432,7 @@
           <t>E | 910呎 (3房)
 $3325万
 $36,533/呎
-(13年-11月)</t>
+(13年-11月-17日)</t>
         </is>
       </c>
     </row>
@@ -47447,7 +47447,7 @@
           <t>A | 949呎 (3房)
 $2885万
 $30,400/呎
-(13年-11月)</t>
+(13年-11月-03日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -47455,7 +47455,7 @@
           <t>B | 1093呎 (4+房)
 $4694万
 $42,941/呎
-(12年-05月)</t>
+(12年-05月-30日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -47463,7 +47463,7 @@
           <t>C | 1608呎 (4+房)
 $6110万
 $38,000/呎
-(10年-11月)</t>
+(10年-11月-14日)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -47471,7 +47471,7 @@
           <t>D | 1070呎 (4+房)
 $3853万
 $36,010/呎
-(10年-12月)</t>
+(10年-12月-12日)</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -47479,7 +47479,7 @@
           <t>E | 913呎 (3房)
 $3378万
 $36,999/呎
-(13年-11月)</t>
+(13年-11月-11日)</t>
         </is>
       </c>
     </row>
@@ -47494,7 +47494,7 @@
           <t>A | 963呎 (3房)
 $2866万
 $29,764/呎
-(13年-11月)</t>
+(13年-11月-04日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -47502,7 +47502,7 @@
           <t>B | 1118呎 (4+房)
 $4470万
 $39,982/呎
-(12年-04月)</t>
+(12年-04月-26日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -47510,7 +47510,7 @@
           <t>C | 1580呎 (4+房)
 $5671万
 $35,892/呎
-(10年-03月)</t>
+(10年-03月-17日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -47518,7 +47518,7 @@
           <t>D | 1070呎 (4+房)
 $3598万
 $33,626/呎
-(10年-06月)</t>
+(10年-06月-01日)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -47526,7 +47526,7 @@
           <t>E | 913呎 (3房)
 $3356万
 $36,760/呎
-(13年-11月)</t>
+(13年-11月-11日)</t>
         </is>
       </c>
     </row>
@@ -47541,7 +47541,7 @@
           <t>A | 949呎 (3房)
 $2848万
 $30,009/呎
-(13年-11月)</t>
+(13年-11月-05日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -47549,7 +47549,7 @@
           <t>B | 1118呎 (4+房)
 $4246万
 $37,983/呎
-(11年-07月)</t>
+(11年-07月-20日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -47557,7 +47557,7 @@
           <t>C | 1580呎 (4+房)
 $5360万
 $33,924/呎
-(10年-01月)</t>
+(10年-01月-24日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -47565,7 +47565,7 @@
           <t>D | 1070呎 (4+房)
 $3519万
 $32,885/呎
-(10年-05月)</t>
+(10年-05月-03日)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -47573,7 +47573,7 @@
           <t>E | 935呎 (3房)
 $3266万
 $34,929/呎
-(13年-11月)</t>
+(13年-11月-11日)</t>
         </is>
       </c>
     </row>
@@ -47588,7 +47588,7 @@
           <t>A | 949呎 (3房)
 $2829万
 $29,814/呎
-(13年-11月)</t>
+(13年-11月-03日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -47596,7 +47596,7 @@
           <t>B | 1118呎 (4+房)
 $4095万
 $36,624/呎
-(11年-06月)</t>
+(11年-06月-08日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -47604,7 +47604,7 @@
           <t>C | 1580呎 (4+房)
 $5000万
 $31,646/呎
-(09年-09月)</t>
+(09年-09月-02日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -47612,7 +47612,7 @@
           <t>D | 1091呎 (4+房)
 $3395万
 $31,119/呎
-(10年-03月)</t>
+(10年-03月-14日)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -47620,7 +47620,7 @@
           <t>E | 913呎 (3房)
 $3245万
 $35,539/呎
-(13年-11月)</t>
+(13年-11月-07日)</t>
         </is>
       </c>
     </row>
@@ -47635,7 +47635,7 @@
           <t>A | 949呎 (3房)
 $6411万
 $67,559/呎
-(13年-10月)</t>
+(13年-10月-15日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -47643,7 +47643,7 @@
           <t>B | 1118呎 (4+房)
 $3874万
 $34,651/呎
-(11年-02月)</t>
+(11年-02月-22日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -47651,7 +47651,7 @@
           <t>C | 1608呎 (4+房)
 $4905万
 $30,507/呎
-(09年-09月)</t>
+(09年-09月-16日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -47659,7 +47659,7 @@
           <t>D | 1091呎 (4+房)
 $3007万
 $27,561/呎
-(09年-10月)</t>
+(09年-10月-26日)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -47667,7 +47667,7 @@
           <t>E | 913呎 (3房)
 $3547万
 $38,852/呎
-(13年-11月)</t>
+(13年-11月-26日)</t>
         </is>
       </c>
     </row>
@@ -47682,7 +47682,7 @@
           <t>A | 949呎 (3房)
 $3082万
 $32,471/呎
-(13年-11月)</t>
+(13年-11月-06日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -47690,7 +47690,7 @@
           <t>B | 1093呎 (4+房)
 $3948万
 $36,125/呎
-(11年-07月)</t>
+(11年-07月-07日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -47698,7 +47698,7 @@
           <t>C | 1580呎 (4+房)
 $5253万
 $33,246/呎
-(10年-04月)</t>
+(10年-04月-06日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -47706,7 +47706,7 @@
           <t>D | 1070呎 (4+房)
 $3272万
 $30,575/呎
-(10年-01月)</t>
+(10年-01月-18日)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -47714,7 +47714,7 @@
           <t>E | 935呎 (3房)
 $3213万
 $34,359/呎
-(13年-11月)</t>
+(13年-11月-13日)</t>
         </is>
       </c>
     </row>
